--- a/docs/finalised set 2026.xlsx
+++ b/docs/finalised set 2026.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,10 +134,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -146,6 +142,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -607,7 +610,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>10 distinct dimensions, one item each. 3 items need artwork, 1 recommended.</t>
+          <t>10 dimensions, one item each. 3 items need artwork, 1 recommended.</t>
         </is>
       </c>
     </row>
@@ -663,7 +666,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>8 strength domains — Analytical, Creative, Leadership, Relationship, Execution, Communication, Adaptability, Learning</t>
+          <t>Client taxonomy per option (Technical / Medical / Environmental / Legal / Financial)</t>
         </is>
       </c>
     </row>
@@ -719,7 +722,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>VARK — Visual, Aural, Read/Write, Kinesthetic, Multimodal</t>
+          <t>VARK — Visual, Auditory, Reading/Writing, Kinesthetic, Multimodal</t>
         </is>
       </c>
     </row>
@@ -814,13 +817,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -845,531 +848,531 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Interests</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Only 10 supplied</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Needs 2 more</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Construct</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Needs a decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Personality</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Option E + wording</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Handled — review</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Emotional intelligence</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Scoring model</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Scoring model. Every option on every item is a healthy response naming a DIFFERENT EQ domain, so there is no weak answer to score against and no defensible EQ level. The engine therefore counts which domain the student reaches for and reports a PROFILE; the EQ percentage is left null rather than publishing an out-of-100 figure off one observation per domain. This replaces the live bank's graded 3/2/2/1 model.</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Handled — review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Aptitude</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Dropped items (blueprint caps aptitude at 10)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>item 16 — bicycle at 12 km/h for 30 minutes</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Applied Math duplicates Numerical Reasoning (already covered by Q13).</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>item 20 — drip irrigation, direct cause</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Statement &amp; Cause; good item, cut only because the blueprint caps aptitude at 10.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>block 2 item 11 — wildlife reserve, 480 animals</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Q16 — artwork recommended</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Two-bar column chart — January 1,200 kWh, February 900 kWh, y-axis in kWh. The item is tagged Data Interpretation but gives the figures in prose only.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Q17 — artwork required</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Four-panel strip: (1) plain square, (2) folded in half, (3) folded again, (4) the folded square with a triangular notch cut from one edge. Do not show the unfolded result.</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Q19 — defect, left as supplied</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT — the two keys contradict each other. TECH=3142 gives T=3; ARTS=5678 gives T=7. The marked answer 6571 assumes T=7. Left exactly as supplied. Fix by changing one key word (ARTS=5637 makes T=3 throughout and RATE=6531), or state that each word uses its own key.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Needs a fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Q20 — defect, left as supplied</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT — the answer needs two rules at once (count +2, sides +1), and circle-to-triangle breaks the sides rule, so option D is arguable. Left as supplied. Starting the series at a triangle would resolve it.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Needs a fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Q20 — artwork required</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Three groups drawn left to right — 3 circles, 5 triangles, 7 squares — then a boxed '?'. Counts must be visibly correct so the 3/5/7 progression can be seen, not just read.</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Q21 — defect, left as supplied</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT — the stem lists 456789 twice, so BOTH 456798 and 456879 are unique and the item has two correct answers. Option E is also a stray letter 'e'. Left exactly as supplied. Fix by listing 456789 three times and giving E an 'All are the same' distractor.</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Needs a fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Q22 — artwork required</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Two meshed spur gears labelled 'Gear A' and 'Gear B', a curved arrow on A marked 'clockwise', a '?' above B. This artwork already exists as inline SVG in the live bank (9-10 Set 1, Q22) and is reused.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>dropped: item 16 — bicycle at 12 km/h for 30 minutes</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Applied Math; duplicates the numerical dimension.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>dropped: item 20 — drip irrigation, direct cause</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Statement &amp; Cause; cut only because the count caps at 10.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>dropped: second block item 11 — wildlife reserve, 480 animals</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Numerical Reasoning duplicate.</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>block 2 item 12 — business earns ₹25,000, 20% more</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Financial Reasoning duplicate of Q13's profit calculation.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>block 2 item 13 — football team, 3 goals per match</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>dropped: second block item 12 — business earns ₹25,000, 20% more</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Financial Reasoning; overlaps Q13.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>dropped: second block item 13 — football team, 3 goals per match</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Numerical Reasoning duplicate.</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>dropped: ₹10,000 social impact project</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Cut only because the count caps at 8.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>dropped: long-term problem giving deepest satisfaction</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Cut only because the count caps at 8.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>dropped: one elective course for next term</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Cut only because the count caps at 8; overlaps interests Q10.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>dropped: 48 hours to present a final major project</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Cut only because the count caps at 8.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Learning styles</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Dropped items (blueprint caps at 4)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>item 9 — 'At home, I am easily distracted by:'</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Not a VARK item. It is a distraction inventory, and option C (phone texts) has nothing to do with Read/Write.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>items 1, 3, 4, 5, 6, 8</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Valid items, cut only because the blueprint caps learning styles at 4.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>dropped: item 9 — 'At home, I am easily distracted by:'</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Not a VARK item — it is a distraction inventory, and option C (phone texts) has nothing to do with Reading/Writing. Would have been cut on quality even if the count allowed it.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Learning styles</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>dropped: items 1, 3, 4, 5, 6, 8</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Valid items, cut only because the count caps at 4.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Emotional intelligence</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Dropped items (blueprint caps at 5)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>items 6-10 — praise for shared work; unexpected criticism; little time left; new student; after a hard task</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Valid items, cut only because the blueprint caps EI at 5. Client items 1-5 were kept because they map one-to-one onto the old Q56-Q60 dimensions.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Emotional intelligence</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Scoring model — resolved</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>SCORING RULE — this sheet yields an EQ PROFILE, not an EQ SCORE. Every option on every item is a healthy response (identify the error / stay calm / set a goal / understand them / ask for guidance), so there is no weak answer to score against and no defensible way to derive a high-or-low EQ level. What it does measure cleanly is which of the five domains the student reaches for first. Score it as forced choice: count how often each domain is chosen across the 5 items and report the leading one or two as a tendency. Do NOT publish a percentage or an out-of-100 EQ figure from these 5 items — with one observation per domain a single changed answer would move the result, so it is not reliable enough to quantify. This replaces the old set's graded 3/2/2/1 model, which the engine currently implements; the engine needs switching to domain counting. If you later want a genuine EQ level, that needs low-EQ distractors, which would mean changing the 60-question blueprint.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Decided — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Personality</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Unscored option E — resolved</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>SCORING RULE for option E. 'None of these' is non-scoring by design on all 12 items. Do NOT divide each trait by 12 — normalise it over the number of items the student actually scored on, so a student who picks E a few times still gets a valid profile instead of an artificially flattened one. If a student picks E on more than half the items, suppress the Big Five profile and report it as incomplete rather than publishing a near-zero result. Note also that option texts were expanded from the client's shorthand into full sentences for Class 9-10 readability; the original wording is preserved in 'finalised set 2026 (client original).xlsx'.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Decided — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Personality</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Option wording</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>The client's options were shorthand notes ('Clearest, idea most reliable approach'), not usable by a Class 9-10 student. All 60 options expanded into full sentences with the meaning unchanged. Original wording preserved in the client-original workbook.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Done — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Personality</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Trait weights</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Derived for all 12 items from the client's option meanings, using the old set's convention (primary trait +3, supporting +1/+2). Trait and facet carried over from the old set, except Q28 (Confidence to Initiative) and Q30/Q31 (Empathy and Cooperation swapped to match the client's scenarios).</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Done — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Interests</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>RIASEC codes</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Derived for all 12 items from what each option actually involves (the client sheet gave career matches but no RIASEC letters). Dominant code listed first.</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Done — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Interests</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Scoring rule</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>SCORING RULE — read each option's cluster from its own tag in the 'Career Cluster (per option)' column, not from the option letter. Across this sheet the client's option positions are not consistent: position C is Law on Q1/Q2/Q4 but Engineering on Q3/Q8, and position D is Arts on Q2/Q4/Q5 but Law on Q6/Q8/Q10. Tag-based scoring makes that harmless; positional scoring would mis-assign clusters on roughly half the items.</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Decided — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Interests</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Q7 option C changed</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Client option C (legal protocols / Law &amp; Administration) duplicated option B's cluster, so two of five choices gave the same signal and Science/Agriculture was unmeasured. Replaced with a lab/epidemiology option.</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Changed — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Interests</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Q9 option D narrowed</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Client option D mixed Law and Creative Arts in one choice, making the answer ambiguous between two clusters. Narrowed to media/publishing; Law is covered on six other items.</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Changed — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Q19 cipher fixed</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Client keys contradicted each other (TECH gave T=3, ARTS gave T=7) and the marked answer assumed T=7. Second key changed to ARTS=5637 so T=3 throughout; RATE = 6531.</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Q20 series fixed</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Client series started at circles, so the count rule (+2) and the side rule (+1) disagreed and option D was arguable. Series now starts at a triangle; answer is 9 hexagons.</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Cluster tags retagged</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Six items carried clusters read off the correct answer rather than the skill (coding-decoding tagged 'Genetic Coder', paper-folding tagged 'Orthopedic Specialist', odd-one-out tagged 'Farm Operator'). Retagged from the old bank's dimension-to-cluster table.</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Interests</t>
-        </is>
-      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Source format</t>
+          <t>dropped: items 6-10 — praise for shared work; unexpected criticism; little time left; new student; after a hard task</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>The client interests sheet was a raw CSV paste — question number and text in one cell, options as 'A,text' in a single column, unbalanced quote marks and a stray leading comma on Q1 option C. Restructured into proper columns here.</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1">
+          <t>Valid items, cut only because the count caps at 5. Items 1-5 were kept because they line up one-to-one with the live bank's Q56-Q60 dimensions.</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Over count</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Construct</t>
+          <t>Live questions replaced</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>The client sheet measured career interests, not strengths: all 12 items reused the same Tech / Health / Agri-Eco / Law-Finance buckets as the interests sheet, and every option was prefixed with its own bucket name, which telegraphs the answer. Rebuilt with 8 items covering the 8 strength domains.</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Rebuilt — review</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Junk rows</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Client sheet row 61 contained a stray 'E | E' and row 92 was blank; both dropped. Items were also numbered 11-20 then restarting at 11-15, so 11-15 appeared twice. Renumbered Q13-Q22.</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Correct-answer marks</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Client sheet used two different marks (checkbox in the first block, green tick in the second). Replaced with a single Correct Answer column.</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Images</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>3 items need artwork before launch (Q17 paper-fold, Q20 shape series, Q22 gears) and 1 is recommended (Q16 kWh bar chart). Q22's artwork already exists as inline SVG in the old bank and can be reused.</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Action needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="46" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Engine</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Option count</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>The app scoring code types these items as 'choice4' and reads exactly four options. It must be widened to five before this set can be imported.</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Action needed</t>
+          <t>scripts/import_finalised_set_2026.py writes this set into project/data/*.json (classes 9-10, Set 1). All other life stages and sets are untouched. Previous bank kept as data/*.pre-2026.json.</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1482,7 +1485,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Diagnose community health issues and suggest remedies.</t>
+          <t>Diagnose community health issues and suggest remedies</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1492,12 +1495,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Research local laws and policies, and present solutions to officials.</t>
+          <t>Research local laws, policies, and present solutions to officials</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Create posters, films, and branding for the fair.</t>
+          <t>Create posters, films, and branding for the fair</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1543,7 +1546,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr"/>
@@ -1622,7 +1625,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr"/>
@@ -1701,7 +1704,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr"/>
@@ -1780,7 +1783,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr"/>
@@ -1859,7 +1862,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr"/>
@@ -1938,7 +1941,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1966,7 +1969,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Trace how the infection is spreading — food, water or contact — and test the samples.</t>
+          <t>Study health guidelines, ensure legal protocols, and enforce safety rules.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1976,14 +1979,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Audit food and water supplies, manage logistics, and secure needed funds.</t>
+          <t>Audit food/water supplies, manage logistics, and secure needed funds.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>A · C — Health Science
 B · F — Human &amp; Public Services
-C · G — Science, Nature &amp; Agriculture
+C · F — Human &amp; Public Services
 D · D — Arts, Media &amp; Design
 E · E — Business &amp; Marketing</t>
         </is>
@@ -1992,7 +1995,7 @@
         <is>
           <t>A · Medical &amp; Emergency Health: Emergency Doctor, Epidemiologist, Paramedic
 B · Psychology &amp; Human Resources: Counselor, Psychologist, HR Manager, Social Worker
-C · Science &amp; Public Health: Microbiologist, Epidemiologist, Lab Scientist
+C · Law &amp; Administration: Hospital Administrator, Compliance Officer, Civil Servant
 D · Design &amp; Communication: PR Specialist, Communications Mgr, Visual Designer
 E · Operations &amp; Supply Chain: Supply Chain Manager, Procurement Officer, Logistics Head</t>
         </is>
@@ -2001,7 +2004,7 @@
         <is>
           <t>A · S+R
 B · S+A
-C · I+R
+C · C+S
 D · A+E
 E · C+E</t>
         </is>
@@ -2010,19 +2013,19 @@
         <is>
           <t>A · S+3, R+1
 B · S+3, A+1
-C · I+3, R+2
+C · C+3, S+1
 D · A+3, E+1
 E · C+3, E+2</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (option C replaced)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>CHANGED. The client's option C ('Study health guidelines, ensure legal protocols, enforce safety rules' — Law &amp; Administration) mapped to Human &amp; Public Services, the same cluster as option B, so two of the five choices gave an identical signal and no Science/Agriculture option was offered. Replaced with a laboratory/epidemiology option so all five families appear once. Revert from the client-original file if you prefer the legal-protocols wording.</t>
+          <t>Options B and C both map to Human &amp; Public Services, so two of the five choices give the same cluster signal and no Science/Agriculture option is offered. Left as supplied — scoring reads the per-option cluster tag, so it still works, but this item measures four families rather than five.</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2062,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Restructuring a struggling business to make it highly profitable.</t>
+          <t>Restructuring an struggling business to make it highly profitable.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2100,12 +2103,12 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>Client text read 'an struggling business' — corrected to 'a struggling business'.</t>
+          <t>Option E reads 'an struggling business' in the sheet. Left as supplied — a one-word typo fix.</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2140,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>A newsroom, media studio, or publishing house.</t>
+          <t>A courtroom, law firm, media studio, or publishing house.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2146,89 +2149,6 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>A · Health Sciences: Physician, Clinical Researcher, Surgeon, Medical Technologist
-B · Agriculture &amp; Earth: Forester, Environmental Consultant, Agricultural Scientist
-C · Engineering &amp; Tech: Software Engineer, Mechanical Engineer, Robotics Researcher
-D · Media &amp; Creative Arts: Journalist, Editor, Creative Director, Producer
-E · Business &amp; Finance: Investment Banker, Equity Analyst, Corporate Executive</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>A · S+I
-B · R+I
-C · R+I
-D · A+E
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>A · S+3, I+2
-B · R+3, I+1
-C · R+3, I+3
-D · A+3, E+1
-E · E+3, C+3</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Client 2026 sheet (option D narrowed)</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>CHANGED. The client's option D read 'A courtroom, law firm, media studio, or publishing house', mixing Law and Creative Arts in one choice, so a student picking it was ambiguous between clusters F and D. Narrowed to the media/publishing half. Law is already covered on Q1, Q2, Q4, Q6, Q8 and Q10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="112" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>If you could take a specialized elective course next term, which would you pick?</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Human Physiology, Nutrition, and Clinical Health Basics.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Environmental Science, Crop Care, and Biotechnology.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Python Programming, Electronics, and Applied Mathematics.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>World History, Constitutional Law, and Creative Writing.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Financial Accounting, Entrepreneurship, and Business Marketing.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>A · C — Health Science
 B · G — Science, Nature &amp; Agriculture
@@ -2237,6 +2157,89 @@
 E · E — Business &amp; Marketing</t>
         </is>
       </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>A · Health Sciences: Physician, Clinical Researcher, Surgeon, Medical Technologist
+B · Agriculture &amp; Earth: Forester, Environmental Consultant, Agricultural Scientist
+C · Engineering &amp; Tech: Software Engineer, Mechanical Engineer, Robotics Researcher
+D · Law &amp; Creative Arts: Advocate, Journalist, Editor, Creative Director
+E · Business &amp; Finance: Investment Banker, Equity Analyst, Corporate Executive</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>A · S+I
+B · R+I
+C · R+I
+D · A+E+S
+E · E+C</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>A · S+3, I+2
+B · R+3, I+1
+C · R+3, I+3
+D · A+2, E+2, S+1
+E · E+3, C+3</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>finalised set 2026</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Option D names both Law and Creative Arts, so a student picking it is ambiguous between clusters F and D. Left as supplied and tagged F; split the option if you want a clean signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>If you could take a specialized elective course next term, which would you pick?</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Human Physiology, Nutrition, and Clinical Health Basics.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Environmental Science, Crop Care, and Biotechnology.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Python Programming, Electronics, and Applied Mathematics.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>World History, Constitutional Law, and Creative Writing.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Financial Accounting, Entrepreneurship, and Business Marketing.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>A · C — Health Science
+B · G — Science, Nature &amp; Agriculture
+C · B — Information Technology
+D · F — Human &amp; Public Services
+E · E — Business &amp; Marketing</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>A · Health &amp; Allied Sciences: Dietitian, Physiotherapist, Sports Medicine Specialist
@@ -2266,7 +2269,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr"/>
@@ -2279,78 +2282,78 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Your school has one slot left in the district science-and-innovation expo. Which entry would you put your name to?</t>
+          <t>A company offers ten students a one-month paid internship. Which team would you ask to join?</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>A low-cost device that screens for anaemia without taking blood.</t>
+          <t>The team working out why the product keeps failing.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>A soil-health sensor that tells farmers exactly what their field is missing.</t>
+          <t>The team redesigning how the product looks and feels.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>An app that maps and reports unsafe road stretches around the school.</t>
+          <t>The team training new users and answering their questions.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>A short documentary on a local craft that is disappearing.</t>
+          <t>The team tracking costs, stock and delivery schedules.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>A costed business plan to take a student product to real customers.</t>
+          <t>The team testing whether the product is safe for people to use.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
+          <t>A · B — Information Technology
+B · D — Arts, Media &amp; Design
+C · F — Human &amp; Public Services
+D · E — Business &amp; Marketing
+E · C — Health Science</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>A · Health &amp; Medical: Biomedical Engineer, Pathologist, Public Health Researcher
-B · Agriculture &amp; Earth Sciences: Soil Scientist, Agricultural Engineer, Agronomist
-C · Engineering &amp; Tech: Software Developer, Data Analyst, Civil Engineer
-D · Arts, Media &amp; Design: Filmmaker, Photographer, Journalist
-E · Business, Finance &amp; Mgmt: Entrepreneur, Financial Analyst, Marketing Manager</t>
+          <t>A · Research Scientist, AI Engineer, Software Engineer
+B · Architect, UX Designer, Graphic Designer
+C · Teacher, Psychologist, Lawyer
+D · Business Manager, Chartered Accountant, Operations Manager
+E · Clinical Research Associate, Pharmacologist, Quality &amp; Safety Officer</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>A · I+S
-B · R+I
-C · I+R+S
-D · A
-E · E+C</t>
+          <t>A · I+R
+B · A
+C · S+E
+D · C+E
+E · I+C</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>A · I+3, S+2
-B · R+3, I+2
-C · I+3, R+1, S+1
-D · A+3
-E · E+3, C+2</t>
+          <t>A · I+3, R+2
+B · A+3
+C · S+3, E+3
+D · C+3, E+3
+E · I+3, C+2</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Authored — please review</t>
+          <t>kept from live bank — sheet supplies only 10 interests questions</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>Authored to bring interests up to the blueprint count of 12. Follows the client's 5-family format.</t>
+          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
         </is>
       </c>
     </row>
@@ -2362,98 +2365,82 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Ten years from now a magazine profiles you. Which headline would you be happiest to read?</t>
+          <t>Your school is starting a student-run magazine and website. Which role would you take?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>“The doctor who brought specialist care to villages that had none.”</t>
+          <t>Research the stories, check the facts, and build the website.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>“The scientist who made a drought-hit district farm again.”</t>
+          <t>Design the layout, illustrations, photographs, and cover art.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>“The engineer behind the system half the country now uses.”</t>
+          <t>Interview people, build the writing team, and reply to readers.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>“The film-maker whose first feature changed the conversation.”</t>
+          <t>Handle advertising, budgets, and the publishing schedule.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>“The founder who built a company out of a school project.”</t>
+          <t>Cover the health, fitness and wellbeing section for students.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
+          <t>A · B — Information Technology
+B · D — Arts, Media &amp; Design
+C · F — Human &amp; Public Services
+D · E — Business &amp; Marketing
+E · C — Health Science</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>A · Health &amp; Medical: Physician, Public Health Specialist, Surgeon
-B · Agriculture &amp; Earth Sciences: Agricultural Scientist, Botanist, Environmental Scientist
-C · Engineering &amp; Tech: Software Architect, Systems Engineer, AI Engineer
-D · Arts, Media &amp; Design: Filmmaker, Creative Director, Writer
-E · Business &amp; Entrepreneurship: Founder/CEO, Business Strategist, Investor</t>
+          <t>A · Software Engineer, Data Analyst, Research Scientist
+B · Graphic Designer, Animator, Product Designer
+C · Teacher, Lawyer, Psychologist
+D · Business Manager, Financial Analyst, Digital Marketer
+E · Health Journalist, Public Health Educator, Medical Writer</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>A · S+I
-B · I+R
-C · I+R
-D · A
-E · E+C</t>
+          <t>A · I+R
+B · A
+C · S+E
+D · C+E
+E · S+A+I</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>A · S+3, I+2
-B · I+3, R+2
-C · I+3, R+2
-D · A+3
-E · E+3, C+1</t>
+          <t>A · I+3, R+2
+B · A+3
+C · S+3, E+2
+D · C+3, E+2
+E · S+2, A+2, I+1</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Authored — please review</t>
+          <t>kept from live bank — sheet supplies only 10 interests questions</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Authored to bring interests up to the blueprint count of 12. Follows the client's 5-family format.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>SCORING RULE — read each option's cluster from its own tag in the 'Career Cluster (per option)' column, not from the option letter. Across this sheet the client's option positions are not consistent: position C is Law on Q1/Q2/Q4 but Engineering on Q3/Q8, and position D is Arts on Q2/Q4/Q5 but Law on Q6/Q8/Q10. Tag-based scoring makes that harmless; positional scoring would mis-assign clusters on roughly half the items.</t>
+          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B15:M15"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2477,11 +2464,11 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2597,7 +2584,7 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2619,24 +2606,20 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Engineering, Finance, Analytics</t>
+          <t>Business, Finance &amp; Law</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Engineer, Chartered Accountant, Data Scientist, Economist</t>
+          <t>Chartered Accountant (CA), Financial Analyst, Investment Banker</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 11)</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>Retagged. Client tag was 'Business, Finance &amp; Law / CA, Financial Analyst, Investment Banker' — kept the finance thrust but widened to the clusters numerical reasoning actually predicts.</t>
-        </is>
-      </c>
+          <t>finalised set 2026 item 11</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="104" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2674,7 +2657,7 @@
           <t>All researchers are science teachers.</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2696,24 +2679,20 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>IT, Engineering, Research, Law</t>
+          <t>Business, Finance &amp; Law</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Lawyer, Research Scientist, AI Engineer</t>
+          <t>Corporate Lawyer, Compliance Officer, Risk Auditor</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 12)</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>Retagged from 'Business, Finance &amp; Law' — syllogistic reasoning predicts IT/research as strongly as law.</t>
-        </is>
-      </c>
+          <t>finalised set 2026 item 12</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="104" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2751,7 +2730,7 @@
           <t>Tractor</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -2768,27 +2747,27 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Supporting illustration: five small line icons, one per option (laptop, stethoscope, ledger, palette, tractor).</t>
+          <t>Five small line icons, one per option (laptop, stethoscope, ledger, palette, tractor).</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Education, Law, Media</t>
+          <t>Society, Nature &amp; Public Service</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Teacher, Lawyer, Journalist, Editor</t>
+          <t>Agricultural Engineer, Farm Operator</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 13)</t>
+          <t>finalised set 2026 item 13</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Retagged. Client tag was 'Society, Nature &amp; Public Service / Agricultural Engineer, Farm Operator', which was read off the correct answer (Tractor) rather than the skill. Verbal classification predicts language-heavy fields.</t>
+          <t>Cluster tag follows the correct answer (Tractor) rather than the skill being tested. Left as supplied.</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2779,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>School electricity usage dropped from 1,200 kWh in January to 900 kWh in February. What is the percentage reduction?</t>
+          <t>School electricity usage dropped from 1,200 kWh in Jan to 900 kWh in Feb. What is the percentage reduction?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2828,7 +2807,7 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2838,34 +2817,34 @@
           <t>Data Interpretation</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Two-bar column chart — January 1,200 kWh and February 900 kWh, y-axis labelled kWh. Needed so the student reads the figures off a display rather than out of prose, which is what Data Interpretation means.</t>
+          <t>Two-bar column chart — January 1,200 kWh, February 900 kWh, y-axis in kWh. The item is tagged Data Interpretation but gives the figures in prose only.</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Finance, AI, Business Analytics</t>
+          <t>Health &amp; Life Sciences</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Data Analyst, Actuary, Economist, Business Analyst</t>
+          <t>Environmental Health Specialist, Bio-Statistician</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 14)</t>
+          <t>finalised set 2026 item 14</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Retagged from 'Health &amp; Life Sciences / Environmental Health Specialist, Bio-Statistician', which did not follow from an electricity-usage item. Chart still to be drawn.</t>
+          <t>Cluster tag (Health &amp; Life Sciences) does not follow from an electricity-usage item. Left as supplied.</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2856,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A square piece of paper is folded twice and a single triangular punch is made through all the layers. When the paper is unfolded, how many punched holes appear?</t>
+          <t>A square piece of paper is folded twice and a triangle punch is made. When unfolded, how many punches appear?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2905,7 +2884,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2915,34 +2894,34 @@
           <t>Spatial Reasoning</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Four-panel strip: (1) plain square, (2) folded in half, (3) folded in half again, (4) the folded square with a triangular notch cut from one edge. Do not show the unfolded result.</t>
+          <t>Four-panel strip: (1) plain square, (2) folded in half, (3) folded again, (4) the folded square with a triangular notch cut from one edge. Do not show the unfolded result.</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Architecture, Civil, Mechanical</t>
+          <t>Health &amp; Life Sciences</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Architect, Civil Engineer, Pilot, Surgeon</t>
+          <t>Orthopedic Specialist, Diagnostic Technician</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 15)</t>
+          <t>finalised set 2026 item 15</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Client marked this '(visual item)' — artwork is mandatory, the item cannot be answered without it. Retagged from 'Health &amp; Life Sciences / Orthopedic Specialist', which did not follow from paper folding.</t>
+          <t>Marked '(visual item)' in the sheet — artwork is mandatory. Cluster tag does not follow from paper folding.</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2961,7 @@
           <t>Policy</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3004,24 +2983,20 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Law, Education, Media</t>
+          <t>Business, Finance &amp; Law</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Lawyer, Teacher, Journalist, Psychologist</t>
+          <t>High Court Lawyer, Magistrate, Corporate Arbitrator</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 17)</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>Retagged from 'Business, Finance &amp; Law' — analogy reasoning is a language aptitude, so education and media belong alongside law.</t>
-        </is>
-      </c>
+          <t>finalised set 2026 item 17</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="104" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -3031,35 +3006,35 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>If TECH is written as 3142 and ARTS is written as 5637, how is RATE written?</t>
+          <t>If TECH is written as 3142, and ARTS is written as 5678, how is RATE written?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+          <t>8714</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3081,22 +3056,22 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>IT, Cryptography, Research</t>
+          <t>Health &amp; Life Sciences</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Cybersecurity Analyst, Data Scientist</t>
+          <t>Genetic Coder, Bioinformatics Specialist</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 18, corrected)</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>FIXED. The client keys contradicted each other: TECH=3142 gives T=3 but ARTS=5678 gives T=7, and the marked answer 6571 silently assumed T=7. Second key changed to ARTS=5637 so T=3 throughout (A=5, R=6, T=3, S=7), making RATE = 6531 the single defensible answer. Options rewritten around it; correct answer stays at B. Also retagged from 'Health &amp; Life Sciences / Genetic Coder'.</t>
+          <t>finalised set 2026 item 18</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>DEFECT — the two keys contradict each other. TECH=3142 gives T=3; ARTS=5678 gives T=7. The marked answer 6571 assumes T=7. Left exactly as supplied. Fix by changing one key word (ARTS=5637 makes T=3 throughout and RATE=6531), or state that each word uses its own key.</t>
         </is>
       </c>
     </row>
@@ -3108,35 +3083,35 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A series shows 3 triangles, then 5 squares, then 7 pentagons. What shape and count come next?</t>
+          <t>A series shows 3 circles, 5 triangles, 7 squares, ?. What shape and count come next?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>8 Hexagons</t>
+          <t>8 Circles</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t>9 Triangles</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
           <t>9 Pentagons</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>9 Hexagons</t>
-        </is>
-      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>10 Heptagons</t>
+          <t>10 Hexagons</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>11 Hexagons</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+          <t>11 Lines</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3146,34 +3121,34 @@
           <t>Abstract Reasoning</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Three groups drawn left to right — 3 triangles, 5 squares, 7 pentagons — then a boxed '?'. Counts must be visibly correct so the 3/5/7 progression can be seen, not just read.</t>
+          <t>Three groups drawn left to right — 3 circles, 5 triangles, 7 squares — then a boxed '?'. Counts must be visibly correct so the 3/5/7 progression can be seen, not just read.</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Design, AI, Innovation</t>
+          <t>Business, Finance &amp; Law</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Architect, UX Designer, Product Designer, AI Engineer</t>
+          <t>Strategic Analyst, Market Forecaster</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 19, corrected)</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>FIXED. The client series started at circles (3 circles, 5 triangles, 7 squares), so the two rules disagreed — count went +2 but the side-count rule broke at circle-to-triangle, leaving D arguable. Series now starts at a triangle: counts +2 and sides +1 both hold cleanly, giving 9 hexagons. Correct answer stays at C. Also retagged from 'Business, Finance &amp; Law'.</t>
+          <t>finalised set 2026 item 19</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>DEFECT — the answer needs two rules at once (count +2, sides +1), and circle-to-triangle breaks the sides rule, so option D is arguable. Left as supplied. Starting the series at a triangle would resolve it.</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3160,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Which number is different?</t>
+          <t>Which number is different? 456789, 456798, 456879, 456789</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3195,25 +3170,25 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>456798</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>456879</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>456789</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>456879</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>456789</t>
-        </is>
-      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>All are the same</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3230,27 +3205,27 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Supporting illustration: the five choices set in a monospaced vertical stack so digits align column by column.</t>
+          <t>The five choices in a monospaced vertical stack so digits align column by column.</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Healthcare, Finance, Quality</t>
+          <t>Healthcare &amp; Finance</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Doctor, Pharmacist, Auditor, QA Engineer</t>
+          <t>Pharmacist, Auditor</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 14, corrected)</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>FIXED. The client stem listed 456789, 456798, 456879, 456789 — because 456789 appeared twice, both 456798 and 456879 were unique, so the item had two correct answers. Option E was also the stray letter 'e'. Rewritten to the old set's pattern: three identical values, one different, plus an 'All are the same' distractor.</t>
+          <t>finalised set 2026 item 14 (second block)</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>DEFECT — the stem lists 456789 twice, so BOTH 456798 and 456879 are unique and the item has two correct answers. Option E is also a stray letter 'e'. Left exactly as supplied. Fix by listing 456789 three times and giving E an 'All are the same' distractor.</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3265,7 @@
           <t>Cannot say</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3300,29 +3275,29 @@
           <t>Mechanical Reasoning</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Two meshed spur gears side by side, labelled 'Gear A' and 'Gear B'. A curved arrow on Gear A marked 'clockwise'; a '?' above Gear B. This artwork already exists as inline SVG in the old aptitude bank (9-10 Set 1, Q22) and can be reused as-is.</t>
+          <t>Two meshed spur gears labelled 'Gear A' and 'Gear B', a curved arrow on A marked 'clockwise', a '?' above B. This artwork already exists as inline SVG in the live bank (9-10 Set 1, Q22) and is reused.</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Mechanical, Robotics, Defence</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Mechanical Engineer, Robotics Engineer, Aerospace Engineer</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 15)</t>
+          <t>finalised set 2026 item 15 (second block)</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
@@ -3351,8 +3326,8 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3417,7 +3392,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1">
+    <row r="2" ht="96" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Q23</t>
@@ -3425,32 +3400,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>You have one weekend to prepare a project on an unfamiliar topic. By Saturday evening you still have several possible directions. What would you most likely do?</t>
+          <t>One weekend to prep a project on an unfamiliar topic; by Saturday evening still have several directions. What would you most likely do?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Go with the most unusual idea, even if it might not work.</t>
+          <t>Most unusual idea, even if risky</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Go with the clearest, most reliable approach.</t>
+          <t>Clearest, idea most reliable approach</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Talk the options through with classmates before choosing.</t>
+          <t>Discuss options with classmates</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Combine the best parts of several different sources.</t>
+          <t>Combine ideas from different sources</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -3465,8 +3440,8 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>A · O+3, S+1
-B · C+3, S+1
+          <t>A · O+3
+B · C+3
 C · E+2, A+2
 D · O+3, C+1
 E · not scored</t>
@@ -3474,16 +3449,16 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>Client option B read 'Clearest, idea most reliable approach' — the stray 'idea' looked like a typo and has been dropped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="100" customHeight="1">
+          <t>Option B reads 'Clearest, idea most reliable approach' — a stray word. Left as supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="96" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Q24</t>
@@ -3491,32 +3466,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Your school is holding an exhibition and you must choose one project. Which would you most enjoy building?</t>
+          <t>School exhibition, must choose one project. Which would you most enjoy building?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>A project that challenges how people normally think.</t>
+          <t>Challenges conventional thinking</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>A carefully planned project that I have tested properly.</t>
+          <t>Carefully planned, tested project</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>An interactive project that visitors can take part in.</t>
+          <t>Interactive, participatory project</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A visually creative project that people will remember.</t>
+          <t>Visually creative project</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -3540,12 +3515,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="100" customHeight="1">
+    <row r="4" ht="96" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Q25</t>
@@ -3553,32 +3528,32 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>An assignment is due in two weeks, but an unexpected event cuts down your study days. What would you most likely do?</t>
+          <t>Assignment due in two weeks, but an unexpected event cuts your study days. What would you most likely do?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Adjust my schedule and follow the revised plan.</t>
+          <t>Adjust schedule, follow revised plan</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Rethink the best approach before starting again.</t>
+          <t>Rethink best approach before restarting</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Work longer hours to catch up.</t>
+          <t>Work longer hours to catch up</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Study with others to stay on track.</t>
+          <t>Study with others to stay on track</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -3602,12 +3577,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
     </row>
-    <row r="5" ht="100" customHeight="1">
+    <row r="5" ht="96" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Q26</t>
@@ -3615,32 +3590,32 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>After an hour studying a hard chapter you still don't understand it. What usually happens next?</t>
+          <t>After an hour studying a hard chapter, still don't understand it. What usually happens next?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>I try a different way of studying it.</t>
+          <t>Try a different study method</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>I take a break and come back to it later.</t>
+          <t>Take a break, return later</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>I ask someone to explain it to me.</t>
+          <t>Ask someone to explain</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>I keep practising even if the theory is still unclear.</t>
+          <t>Keep practicing despite unclear theory</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -3664,12 +3639,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Q27</t>
@@ -3682,27 +3657,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Keeping everything organised and on track.</t>
+          <t>Keep everything organized</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Suggesting new ideas and solutions.</t>
+          <t>Suggest new ideas/solutions</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Keeping everyone coordinated and motivated.</t>
+          <t>Keep everyone coordinated &amp; motivated</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Dealing with the most urgent problem first.</t>
+          <t>Tackle the most urgent problem first</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -3726,12 +3701,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="96" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Q28</t>
@@ -3739,32 +3714,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>You arrive early for a workshop and most students are already talking. What would you most likely do?</t>
+          <t>Arrive early for a workshop; most students already talking. What would you most likely do?</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Join the conversation naturally.</t>
+          <t>Join conversation naturally</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Watch for a while before joining in.</t>
+          <t>Observe before joining</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Start talking once I notice a shared interest.</t>
+          <t>Talk if shared interests noticed</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Wait until someone includes me.</t>
+          <t>Wait to be included</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -3788,16 +3763,16 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Facet changed from the old set's 'Confidence'. The old Q28 measured confidence through public speaking; this scenario measures whether the student initiates socially, which is distinct from Q29's question about how the first week turned out. Calling it Initiative keeps Q28 and Q29 from measuring the same thing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1">
+          <t>Facet recorded as Initiative rather than the old set's Confidence: this scenario is about starting a conversation, which keeps it distinct from Q29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="96" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Q29</t>
@@ -3805,32 +3780,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>You joined a new class for a semester. By the end of the first week, what is most likely true?</t>
+          <t>Joined a new class for a semester. By end of first week, what's most likely true?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>I have already introduced myself to a lot of people.</t>
+          <t>Already introduced myself to many</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>I have spoken mainly when I needed to.</t>
+          <t>Spoke mainly when needed</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>I have connected with a few people like me.</t>
+          <t>Connected with a few similar people</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>I have focused on settling in first.</t>
+          <t>Focused on settling in first</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -3854,12 +3829,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
     </row>
-    <row r="9" ht="100" customHeight="1">
+    <row r="9" ht="96" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Q30</t>
@@ -3867,32 +3842,32 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>During a team activity, two members disagree on how to complete the work. What would you naturally do?</t>
+          <t>During a team activity, two members disagree on how to complete work. What would you naturally do?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Help both sides understand each other.</t>
+          <t>Help both sides understand each other</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Combine the strongest parts of both ideas.</t>
+          <t>Combine strongest parts of both ideas</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Let the group decide and focus on my own task.</t>
+          <t>Let group decide, focus on own task</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Choose whichever option is most practical.</t>
+          <t>Choose most practical option</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -3916,16 +3891,16 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Facets swapped relative to the old set: old Q30 measured Empathy and old Q31 Cooperation. Mapped to match the client's new scenarios, which are the other way round.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
+          <t>Facets are the reverse of the old set here: old Q30 measured Empathy, old Q31 Cooperation. Mapped to match the sheet's scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Q31</t>
@@ -3933,32 +3908,32 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A teammate is falling behind and the deadline is approaching. What feels most natural?</t>
+          <t>A teammate is falling behind, deadline approaching. What feels most natural?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Support them, but encourage them to do their own part.</t>
+          <t>Support them, encourage their own effort</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Adjust the plan so everyone contributes fairly.</t>
+          <t>Adjust plan for fair contribution</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Finish part of their task to help the team.</t>
+          <t>Finish part of task to help team</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Focus on my own responsibilities first.</t>
+          <t>Focus on own responsibilities first</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -3982,16 +3957,16 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>Facets swapped relative to the old set — see Q30.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1">
+          <t>See Q30 — facets swapped relative to the old set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Q32</t>
@@ -3999,32 +3974,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Your result is much lower than expected after working hard. What would you most likely do next?</t>
+          <t>Result is much lower than expected after working hard. What would you most likely do next?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Review my mistakes and adjust my approach.</t>
+          <t>Review mistakes, adjust approach</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Ask for feedback on where I went wrong.</t>
+          <t>Ask for feedback</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Take a short break, then start again.</t>
+          <t>Take a short break, restart</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Accept the result and keep working steadily.</t>
+          <t>Accept result, keep working steadily</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -4048,12 +4023,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="100" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Q33</t>
@@ -4061,32 +4036,32 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Just before presenting, you realize an important part is missing. What is your first reaction?</t>
+          <t>Just before presenting, realize an important part is missing. First reaction?</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Quickly find another way to explain it.</t>
+          <t>Quickly find another way to explain</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pause, understand the situation, then continue.</t>
+          <t>Pause, understand, then continue</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Ask someone nearby for help.</t>
+          <t>Ask someone nearby for help</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Carry on and adapt as I go.</t>
+          <t>Continue and adapt as needed</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -4110,12 +4085,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
     </row>
-    <row r="13" ht="100" customHeight="1">
+    <row r="13" ht="96" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Q34</t>
@@ -4123,32 +4098,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>You have four internship offers with the same salary and growth. Which would you most enjoy?</t>
+          <t>Four internship offers with same salary/growth. Which would you most enjoy?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>One where I learn something completely new.</t>
+          <t>Learn something completely new</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>One where I create original ideas, designs or solutions.</t>
+          <t>Create original ideas/designs/solutions</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>One where I work closely with people and help teams.</t>
+          <t>Work closely with people, help teams</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>One where I improve systems and boost efficiency.</t>
+          <t>Improve systems, boost efficiency</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>None of these.</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -4172,21 +4147,21 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (options expanded)</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
     </row>
     <row r="14"/>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>SCORING RULE for option E. 'None of these' is non-scoring by design on all 12 items. Do NOT divide each trait by 12 — normalise it over the number of items the student actually scored on, so a student who picks E a few times still gets a valid profile instead of an artificially flattened one. If a student picks E on more than half the items, suppress the Big Five profile and report it as incomplete rather than publishing a near-zero result. Note also that option texts were expanded from the client's shorthand into full sentences for Class 9-10 readability; the original wording is preserved in 'finalised set 2026 (client original).xlsx'.</t>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
         </is>
       </c>
     </row>
@@ -4204,22 +4179,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4260,36 +4236,41 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Strength Domains Measured</t>
+          <t>Strength Domain(s) Measured (sheet)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Strength Domain (per option)</t>
+          <t>Client Domain (per option)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Strength Domain — engine (derived)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Strength Weights (per option)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Career Clusters</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Example Professions</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="110" customHeight="1">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Source (per option)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="112" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Q35</t>
@@ -4297,190 +4278,313 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Your team has six weeks to build an entry for a national school challenge. In the first week, what are you doing?</t>
+          <t>Your school is leading a District Youth Summit. Which track do you choose to direct?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Breaking the brief down and working out what actually wins marks.</t>
+          <t>Smart Tech &amp; AI: Coding automation tools or robotics exhibits.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Sketching an idea nobody else will have thought of.</t>
+          <t>Health &amp; Bio-Care: Demonstrating medical diagnostic tools &amp; first-aid.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Sorting out who does what, and making sure nobody drops out.</t>
+          <t>Eco-Agri Solutions: Setting up hydroponic farming &amp; soil tests.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Turning the deadline into a week-by-week plan and starting task one.</t>
+          <t>Law &amp; Public Policy: Hosting mock parliament &amp; debating policies.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Reading up on the subject until I know it better than the rest of the team.</t>
+          <t>Media &amp; Design: Producing the summit's films, posters and live coverage.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Analytical, Creative, Leadership, Execution, Learning</t>
+          <t>Technical, Medical, Environmental, Legal/Policy</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>A · Technical
+B · Medical
+C · Environmental
+D · Legal/Policy
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
           <t>A · Analytical
-B · Creative
-C · Leadership
-D · Execution
-E · Learning</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+B · Relationship
+C · Execution
+D · Communication
+E · Creative</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical+3, Execution+1
+B · Relationship+3, Analytical+1
+C · Execution+3, Learning+1
+D · Communication+3, Leadership+1
+E · Creative+3, Communication+1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>STEM &amp; AI, Health &amp; Life Sciences, Agriculture &amp; Earth Sciences, Law &amp; Public Service</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer, Medical Doctor, Agricultural Engineer, Lawyer / IAS Officer</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q36</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A local neighborhood faces severe water logging and waste management issues. What is your first step?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Build a smart sensor prototype to monitor drainage flow.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Conduct water purity &amp; health risk testing for residents.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Draft a legal petition &amp; campaign to municipal authorities.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Launch a local micro-funded recycling business model.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Run an awareness drive with posters, films and street theatre.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Engineering, Clinical/Bio-Health, Advocacy/Legal, Financial/Business</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>A · Engineering
+B · Clinical/Bio-Health
+C · Advocacy/Legal
+D · Financial/Business
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical
+B · Analytical
+C · Communication
+D · Leadership
+E · Creative</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical+3, Execution+1
+B · Analytical+3, Learning+1
+C · Communication+3, Leadership+1
+D · Leadership+3, Execution+1
+E · Creative+3, Communication+1</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Core Engineering, Public Health, Law &amp; Governance, Commerce &amp; Business</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Civil Engineer, Epidemiologist, Environmental Lawyer, Business Manager</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Your school gets funding for one new modern learning facility. Which proposal do you champion?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Computer &amp; Tech R&amp;D Lab: 3D printers, coding kits, &amp; server gear.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Biology &amp; Medical Lab: Advanced microscopes &amp; human anatomy models.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Greenhouse &amp; Soil Lab: Eco-gardening, crop genetics, &amp; bio-fertilizers.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Debate &amp; Legal Clinic: Courtroom setup for legal &amp; civic studies.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Media &amp; Design Studio: cameras, editing suites and a design lab.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Analytical, Diagnostic, Ecological, Civic/Communicative</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical
+B · Diagnostic
+C · Ecological
+D · Civic/Communicative
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical
+B · Analytical
+C · Execution
+D · Communication
+E · Creative</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>A · Analytical+3, Learning+1
-B · Creative+3, Analytical+1
-C · Leadership+3, Relationship+1
-D · Execution+3, Analytical+1
-E · Learning+3, Analytical+1</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Engineering &amp; Technology, Business &amp; Management, Design &amp; Innovation, Research</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer, Scientist, Entrepreneur, Architect, Product Manager</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Q36</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Your class presents to parents tomorrow and the presentation is half finished. What do you take on?</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Checking every fact and figure before it goes on a slide.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Finding an angle that will actually hold the room.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Standing up and delivering it.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Building the slides and fixing the running order.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Keeping everyone calm and working until it is done.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Creative, Communication, Execution, Relationship</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Creative
-C · Communication
-D · Execution
-E · Relationship</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Execution+1
-B · Creative+3, Communication+1
-C · Communication+3, Leadership+1
-D · Execution+3, Creative+1
-E · Relationship+3, Leadership+1</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Media, Education, Human Resources, Public Relations</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Teacher, Marketing Manager, Journalist, HR Manager, PR Specialist</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Q37</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>A new student joins mid-term and is clearly struggling to settle in. What do you do?</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Work out what is actually making it hard for them before doing anything.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Introduce them around and sit with them for a few days.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Raise it with the class so everyone makes an effort.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Set up a buddy rota and make sure it keeps running.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Get them into an activity they would be good at, so people see them differently.</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Relationship, Communication, Execution, Creative</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+B · Analytical+3, Learning+2
+C · Execution+3, Learning+1
+D · Communication+3, Leadership+1
+E · Creative+3, Execution+1</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Life Sciences &amp; Medicine, Agriculture, Law &amp; Social Sciences</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AI Developer, Biotechnologist, Agronomist, Constitutional Lawyer</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q38</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Your class must create a digital platform for Indian students. What primary feature do you design?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>An AI algorithm that solves complex study problems.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Mental health counselling &amp; wellness tracker tools.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>An interactive portal on civic rights, duties, &amp; legal awareness.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>A pocket-money management &amp; micro-investing simulator.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>A creative showcase where students publish art, writing and film.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Technical, Psychological, Civic/Legal, Financial</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>A · Technical
+B · Psychological
+C · Civic/Legal
+D · Financial
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>A · Analytical
 B · Relationship
@@ -4489,407 +4593,404 @@
 E · Creative</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Learning+1
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical+3, Creative+1
+B · Relationship+3, Analytical+1
+C · Communication+3, Learning+1
+D · Execution+3, Analytical+1
+E · Creative+3, Communication+1</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Allied Health &amp; Psychology, Law &amp; Humanities, Finance &amp; Business</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Systems Architect, Clinical Psychologist, Legal Advisor, Financial Planner</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="112" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q39</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Your team enters an Inter-School Community Project competition. Which role do you pick?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical/Tech Lead: Building &amp; repairing hardware tools.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Medical &amp; Wellness Lead: Managing first-aid &amp; health checkups.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Environmental Lead: Designing tree plantation &amp; soil care plans.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Finance Lead: Budgeting, sponsorship, &amp; pitch decks.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Communications Lead: documenting the project and presenting it publicly.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical, Medical, Environmental, Strategic/Financial</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>A · Mechanical
+B · Medical
+C · Environmental
+D · Strategic/Financial
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>A · Execution
+B · Relationship
+C · Execution
+D · Leadership
+E · Communication</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>A · Execution+3, Analytical+1
+B · Relationship+3, Execution+1
+C · Execution+3, Creative+1
+D · Leadership+3, Analytical+1
+E · Communication+3, Creative+1</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics, Healthcare, Agriculture &amp; Ecology, Commerce &amp; Finance</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer, Paramedic / Doctor, Forestry Officer, Chartered Accountant (CA)</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q40</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>If you could shadow a top professional for one week, who would you choose?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>A Lead Developer coding AI applications at a tech giant.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>A Surgeon performing precision operations in a hospital.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>An Agricultural Scientist developing drought-resistant crops.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>A Corporate Lawyer defending major international clients.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>A Creative Director running a design and film studio.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Analytical/Tech, Diagnostic/Medical, Biological/Agri, Logical/Legal</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical/Tech
+B · Diagnostic/Medical
+C · Biological/Agri
+D · Logical/Legal
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical
+B · Execution
+C · Learning
+D · Communication
+E · Creative</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical+3, Learning+2
+B · Execution+3, Analytical+2
+C · Learning+3, Analytical+1
+D · Communication+3, Analytical+1
+E · Creative+3, Leadership+1</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>STEM &amp; Software, Medical Sciences, Agriculture &amp; Bio-Tech, Law &amp; Corporate Services</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Surgeon, Agronomist, Corporate Advocate</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="112" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q41</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Your school newsletter needs a special dedicated column. Which section do you write?</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Tech Byte: Future AI gadgets, coding, &amp; space discoveries.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Body &amp; Mind: Disease prevention, health tips, &amp; sports nutrition.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Earth Watch: Climate action, sustainable farming, &amp; wildlife.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Money &amp; Markets: Stock market basics, saving tips, &amp; startups.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Stage &amp; Screen: film, music, design and student creative work.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Technical, Health/Biological, Ecological, Financial</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>A · Technical
+B · Health/Biological
+C · Ecological
+D · Financial
+E · Creative/Media</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical
+B · Relationship
+C · Learning
+D · Analytical
+E · Creative</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>A · Analytical+3, Communication+1
 B · Relationship+3, Communication+1
-C · Communication+3, Leadership+1
-D · Execution+3, Relationship+1
-E · Creative+3, Relationship+1</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Education, Human Resources, Psychology, Public Service</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Teacher, Counsellor, HR Manager, Social Worker, Psychologist</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="110" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Q38</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Four weeks into a project you realise the approach you chose will not work. What is your first move?</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Trace back to exactly where it started going wrong.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Switch to a different approach and keep moving.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Look up how other people have solved something similar.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Get the team together and rethink it with them.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Rebuild the schedule around a method I know will finish on time.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Adaptability, Learning, Relationship, Execution</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Adaptability
-C · Learning
-D · Relationship
-E · Execution</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Execution+1
-B · Adaptability+3, Execution+1
-C · Learning+3, Analytical+1
-D · Relationship+3, Communication+1
-E · Execution+3, Leadership+1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Research, Consulting, Healthcare, Education</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Doctor, Consultant, Teacher, Research Scientist, Psychologist</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Q39</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Your school gives your group a budget and complete freedom for one project. Which role do you want?</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Deciding what we do, and holding us to it.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Coming up with the idea itself.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Pitching it to the school and to sponsors.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Running the budget, the timeline and the paperwork.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Learning whatever new skill the project turns out to need.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Leadership, Creative, Communication, Execution, Learning</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>A · Leadership
-B · Creative
-C · Communication
+C · Learning+3, Communication+1
+D · Analytical+3, Leadership+1
+E · Creative+3, Communication+1</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Science &amp; Tech, Healthcare, Agriculture &amp; Environment, Business &amp; Economics</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Data Scientist, Nutritionist / Physician, Wildlife Biologist, Investment Banker</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="112" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q42</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>A sudden emergency occurs during a school trip. What is your immediate instinct?</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Fix malfunctioning communications or transport gear.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Provide immediate first-aid &amp; assess physical symptoms.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Consult rules, safety guidelines, &amp; legal protocols.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Manage food/water resources &amp; organize logistics calmly.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Keep everyone calm and handle communication with the group.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Technical, Medical, Administrative, Operations</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>A · Technical
+B · Medical
+C · Administrative
+D · Operations
+E · Interpersonal</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>A · Execution
+B · Execution
+C · Analytical
 D · Execution
-E · Learning</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>A · Leadership+3, Execution+1
-B · Creative+3, Learning+1
-C · Communication+3, Leadership+1
-D · Execution+3, Analytical+1
-E · Learning+3, Adaptability+1</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Business &amp; Entrepreneurship, Marketing, Management</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Entrepreneur, Product Manager, Business Analyst, Marketing Manager</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Q40</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Two people in your group have stopped speaking to each other and the work has stalled. What do you do?</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Talk to each of them separately first.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Get it out in the open with the whole group.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Make a call on the disputed point so we can move on.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Work out which of the two options is actually better on the evidence.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Reshuffle the tasks so they do not have to work together.</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Relationship, Communication, Leadership, Analytical, Adaptability</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>A · Relationship
-B · Communication
-C · Leadership
-D · Analytical
-E · Adaptability</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>A · Relationship+3, Communication+1
-B · Communication+3, Leadership+1
-C · Leadership+3, Execution+1
-D · Analytical+3, Learning+1
-E · Adaptability+3, Execution+1</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Human Resources, Management, Law, Public Administration</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>HR Manager, Project Manager, Lawyer, IAS Officer, Team Leader</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Q41</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>You are handed something broken — an old radio, a bicycle, a piece of code — and told to make it work. How do you start?</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Take it apart methodically and find the fault.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Read up on how it is supposed to work first.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>See whether it could become something better than it was.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Start trying things and adjust as I learn what breaks.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Break it into stages, get the parts I need, and work through to a finish.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Learning, Creative, Adaptability, Execution</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Learning
-C · Creative
-D · Adaptability
-E · Execution</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Execution+1
-B · Learning+3, Analytical+1
-C · Creative+3, Learning+1
-D · Adaptability+3, Creative+1
-E · Execution+3, Analytical+1</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Core Engineering, Innovation, Research &amp; Development</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Mechanical Engineer, Product Designer, AI Engineer, Innovation Consultant</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="110" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Q42</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Looking back at the projects you have enjoyed the most, what usually made them enjoyable?</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Solving a hard problem and finding the answer.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Making something original.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Working with people and getting there together.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Running it well and having it all come off.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Getting genuinely good at something new.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Creative, Relationship, Execution, Learning</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Creative
-C · Relationship
-D · Execution
-E · Learning</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Learning+2
-B · Creative+3, Adaptability+1
-C · Relationship+3, Leadership+2
+E · Relationship</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>A · Execution+3, Analytical+1
+B · Execution+3, Relationship+2
+C · Analytical+3, Execution+1
 D · Execution+3, Leadership+1
-E · Learning+3, Adaptability+1</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Integrated validation — all career clusters</t>
+E · Relationship+3, Communication+2</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Engineering, Healthcare, Business, Design, Research, Education, Government, Media, Finance</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>Authored — please review</t>
+          <t>Core Engineering, Emergency Medicine, Law &amp; Compliance, Operations &amp; Supply Chain</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Operations Engineer, Emergency Doctor, Hospital Administrator, Supply Chain Head</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B11:N11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4904,18 +5005,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4985,7 +5086,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="110" customHeight="1">
+    <row r="2" ht="112" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Q43</t>
@@ -4993,7 +5094,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>School gives you the opportunity to select one special project for the entire year. Which would excite you most?</t>
+          <t>School gives opportunity to select one special project for the entire year. Which would excite you most?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -5018,7 +5119,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Take on a well-defined project with clear steps and a dependable result</t>
+          <t>A well-defined project with clear steps and a dependable result</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -5056,15 +5157,15 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>A · Client 2026 sheet
-B · Client 2026 sheet
-C · Client 2026 sheet
-D · Client 2026 sheet
-E · Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1">
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Q44</t>
@@ -5135,15 +5236,15 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>A · Client 2026 sheet
-B · Client 2026 sheet
-C · Client 2026 sheet
-D · Client 2026 sheet
-E · Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Q45</t>
@@ -5176,7 +5277,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Building a secure, stable career that comfortably supports my family</t>
+          <t>Building a secure, stable career that supports my family well</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -5214,15 +5315,15 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>A · Client 2026 sheet
-B · Client 2026 sheet
-C · Client 2026 sheet
-D · Client 2026 sheet
-E · Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="110" customHeight="1">
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Q46</t>
@@ -5255,7 +5356,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>A challenge with clear rules, where I know exactly what is expected</t>
+          <t>A challenge with clear rules where I know exactly what is expected</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -5293,15 +5394,15 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>A · Client 2026 sheet
-B · Client 2026 sheet
-C · Client 2026 sheet
-D · Client 2026 sheet
-E · Authored — please review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="110" customHeight="1">
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Q47</t>
@@ -5372,11 +5473,11 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>A · Client 2026 sheet
-B · Client 2026 sheet
-C · Client 2026 sheet
-D · Client 2026 sheet
-E · Authored — please review</t>
+          <t>A · finalised set 2026
+B · finalised set 2026
+C · finalised set 2026
+D · finalised set 2026
+E · 5th option added</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5506,7 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5426,12 +5527,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Option B (Aural)</t>
+          <t>Option B (Auditory)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Option C (Read/Write)</t>
+          <t>Option C (Reading/Writing)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -5509,15 +5610,15 @@
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>A · Visual
-B · Aural
-C · Read/Write
+B · Auditory
+C · Reading/Writing
 D · Kinesthetic
 E · Multimodal</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Visual / Aural / Read/Write / Kinesthetic / Multimodal</t>
+          <t>Visual / Auditory / Reading/Writing / Kinesthetic / Multimodal</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -5532,7 +5633,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 2) — matches old Q48 'difficult new concept'</t>
+          <t>finalised set 2026 item 2</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5650,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Look at colourful mind-maps or diagrams</t>
+          <t>Look at colorful mind-maps or diagrams.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Join a study group to discuss topics out loud</t>
+          <t>Join a study group to discuss topics out loud.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5569,21 +5670,21 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Combine diagrams, discussion, notes and practice depending on the subject</t>
+          <t>Mix diagrams, discussion, notes and practice depending on the subject</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>A · Visual
-B · Aural
-C · Read/Write
+B · Auditory
+C · Reading/Writing
 D · Kinesthetic
 E · Multimodal</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Visual / Aural / Read/Write / Kinesthetic / Multimodal</t>
+          <t>Visual / Auditory / Reading/Writing / Kinesthetic / Multimodal</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -5598,7 +5699,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 10) — matches old Q49 'exam preparation'</t>
+          <t>finalised set 2026 item 10</t>
         </is>
       </c>
     </row>
@@ -5641,15 +5742,15 @@
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>A · Visual
-B · Aural
-C · Read/Write
+B · Auditory
+C · Reading/Writing
 D · Kinesthetic
 E · Multimodal</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Visual / Aural / Read/Write / Kinesthetic / Multimodal</t>
+          <t>Visual / Auditory / Reading/Writing / Kinesthetic / Multimodal</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -5664,7 +5765,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 7) — matches old Q50 'new skill outside academics'</t>
+          <t>finalised set 2026 item 7</t>
         </is>
       </c>
     </row>
@@ -5681,22 +5782,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Watch videos of professionals at work</t>
+          <t>Watch videos of professionals at work.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Attend talks and meet counsellors directly</t>
+          <t>Attend talks and meet counsellors directly.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Read guides and articles about professions</t>
+          <t>Read guides and articles about professions.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Visit workplaces or try internships hands-on</t>
+          <t>Visit workplaces or try internships hands-on.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -5707,15 +5808,15 @@
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>A · Visual
-B · Aural
-C · Read/Write
+B · Auditory
+C · Reading/Writing
 D · Kinesthetic
 E · Multimodal</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Visual / Aural / Read/Write / Kinesthetic / Multimodal</t>
+          <t>Visual / Auditory / Reading/Writing / Kinesthetic / Multimodal</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -5730,7 +5831,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet (item 11) — matches old Q51 'career options'</t>
+          <t>finalised set 2026 item 11</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5857,7 @@
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -5805,7 +5906,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Intelligences Measured</t>
+          <t>Intelligence Weights (per option)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -5871,7 +5972,11 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Logical-Mathematical, Visual-Spatial, Linguistic / Interpersonal, Intrapersonal, Bodily-Kinesthetic</t>
+          <t>A · Logical–Mathematical+3, Spatial+1
+B · Spatial+3, Logical–Mathematical+1
+C · Linguistic+3, Interpersonal+2
+D · Intrapersonal+3, Logical–Mathematical+1
+E · Bodily–Kinesthetic+3, Spatial+1</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -5886,7 +5991,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -5937,7 +6042,11 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Logical-Mathematical, Visual-Spatial, Linguistic / Interpersonal, Intrapersonal, Bodily-Kinesthetic</t>
+          <t>A · Logical–Mathematical+3, Spatial+1
+B · Spatial+3, Logical–Mathematical+1
+C · Linguistic+3, Interpersonal+2
+D · Intrapersonal+3, Logical–Mathematical+1
+E · Bodily–Kinesthetic+3, Spatial+1</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -5952,7 +6061,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6112,11 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Logical-Mathematical, Visual-Spatial, Linguistic / Interpersonal, Intrapersonal, Bodily-Kinesthetic</t>
+          <t>A · Logical–Mathematical+3, Spatial+1
+B · Spatial+3, Logical–Mathematical+1
+C · Linguistic+3, Interpersonal+2
+D · Intrapersonal+3, Logical–Mathematical+1
+E · Bodily–Kinesthetic+3, Spatial+1</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -6018,7 +6131,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6182,11 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Logical-Mathematical, Visual-Spatial, Linguistic / Interpersonal, Intrapersonal, Bodily-Kinesthetic</t>
+          <t>A · Logical–Mathematical+3, Spatial+1
+B · Spatial+3, Logical–Mathematical+1
+C · Linguistic+3, Interpersonal+2
+D · Intrapersonal+3, Logical–Mathematical+1
+E · Bodily–Kinesthetic+3, Spatial+1</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -6084,7 +6201,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6277,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Question Dimension (old set)</t>
+          <t>Question Dimension</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -6251,7 +6368,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6439,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6510,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6581,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
@@ -6535,20 +6652,20 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Client 2026 sheet</t>
+          <t>finalised set 2026</t>
         </is>
       </c>
     </row>
     <row r="7"/>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>SCORING RULE — this sheet yields an EQ PROFILE, not an EQ SCORE. Every option on every item is a healthy response (identify the error / stay calm / set a goal / understand them / ask for guidance), so there is no weak answer to score against and no defensible way to derive a high-or-low EQ level. What it does measure cleanly is which of the five domains the student reaches for first. Score it as forced choice: count how often each domain is chosen across the 5 items and report the leading one or two as a tendency. Do NOT publish a percentage or an out-of-100 EQ figure from these 5 items — with one observation per domain a single changed answer would move the result, so it is not reliable enough to quantify. This replaces the old set's graded 3/2/2/1 model, which the engine currently implements; the engine needs switching to domain counting. If you later want a genuine EQ level, that needs low-EQ distractors, which would mean changing the 60-question blueprint.</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Scoring model. Every option on every item is a healthy response naming a DIFFERENT EQ domain, so there is no weak answer to score against and no defensible EQ level. The engine therefore counts which domain the student reaches for and reports a PROFILE; the EQ percentage is left null rather than publishing an out-of-100 figure off one observation per domain. This replaces the live bank's graded 3/2/2/1 model.</t>
         </is>
       </c>
     </row>

--- a/docs/finalised set 2026.xlsx
+++ b/docs/finalised set 2026.xlsx
@@ -71,17 +71,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,26 +128,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -861,10 +861,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+          <t>All 12 interests items are now behaviour-based (see finalised_set_2026_interests_v2.py). The sheet's original 10 named their own career field in the option text, which let a student steer the result; the rewrite hides the signal and rotates option order.</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Needs 2 more</t>
         </is>
@@ -886,7 +886,7 @@
           <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Needs a decision</t>
         </is>
@@ -908,7 +908,7 @@
           <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Handled — review</t>
         </is>
@@ -930,7 +930,7 @@
           <t>Scoring model. Every option on every item is a healthy response naming a DIFFERENT EQ domain, so there is no weak answer to score against and no defensible EQ level. The engine therefore counts which domain the student reaches for and reports a PROFILE; the EQ percentage is left null rather than publishing an out-of-100 figure off one observation per domain. This replaces the live bank's graded 3/2/2/1 model.</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Handled — review</t>
         </is>
@@ -952,7 +952,7 @@
           <t>Two-bar column chart — January 1,200 kWh, February 900 kWh, y-axis in kWh. The item is tagged Data Interpretation but gives the figures in prose only.</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -974,7 +974,7 @@
           <t>Four-panel strip: (1) plain square, (2) folded in half, (3) folded again, (4) the folded square with a triangular notch cut from one edge. Do not show the unfolded result.</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -996,7 +996,7 @@
           <t>DEFECT — the two keys contradict each other. TECH=3142 gives T=3; ARTS=5678 gives T=7. The marked answer 6571 assumes T=7. Left exactly as supplied. Fix by changing one key word (ARTS=5637 makes T=3 throughout and RATE=6531), or state that each word uses its own key.</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Needs a fix</t>
         </is>
@@ -1018,7 +1018,7 @@
           <t>DEFECT — the answer needs two rules at once (count +2, sides +1), and circle-to-triangle breaks the sides rule, so option D is arguable. Left as supplied. Starting the series at a triangle would resolve it.</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Needs a fix</t>
         </is>
@@ -1040,7 +1040,7 @@
           <t>Three groups drawn left to right — 3 circles, 5 triangles, 7 squares — then a boxed '?'. Counts must be visibly correct so the 3/5/7 progression can be seen, not just read.</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -1062,7 +1062,7 @@
           <t>DEFECT — the stem lists 456789 twice, so BOTH 456798 and 456879 are unique and the item has two correct answers. Option E is also a stray letter 'e'. Left exactly as supplied. Fix by listing 456789 three times and giving E an 'All are the same' distractor.</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Needs a fix</t>
         </is>
@@ -1084,7 +1084,7 @@
           <t>Two meshed spur gears labelled 'Gear A' and 'Gear B', a curved arrow on A marked 'clockwise', a '?' above B. This artwork already exists as inline SVG in the live bank (9-10 Set 1, Q22) and is reused.</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -1106,7 +1106,7 @@
           <t>Applied Math; duplicates the numerical dimension.</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1128,7 +1128,7 @@
           <t>Statement &amp; Cause; cut only because the count caps at 10.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1150,7 +1150,7 @@
           <t>Numerical Reasoning duplicate.</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1172,7 +1172,7 @@
           <t>Financial Reasoning; overlaps Q13.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1194,7 +1194,7 @@
           <t>Numerical Reasoning duplicate.</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1216,7 +1216,7 @@
           <t>Cut only because the count caps at 8.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1238,7 +1238,7 @@
           <t>Cut only because the count caps at 8.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1260,7 +1260,7 @@
           <t>Cut only because the count caps at 8; overlaps interests Q10.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1282,7 +1282,7 @@
           <t>Cut only because the count caps at 8.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1304,7 +1304,7 @@
           <t>Not a VARK item — it is a distraction inventory, and option C (phone texts) has nothing to do with Reading/Writing. Would have been cut on quality even if the count allowed it.</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1326,7 +1326,7 @@
           <t>Valid items, cut only because the count caps at 4.</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1348,7 +1348,7 @@
           <t>Valid items, cut only because the count caps at 5. Items 1-5 were kept because they line up one-to-one with the live bank's Q56-Q60 dimensions.</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Over count</t>
         </is>
@@ -1370,7 +1370,7 @@
           <t>scripts/import_finalised_set_2026.py writes this set into project/data/*.json (classes 9-10, Set 1). All other life stages and sets are untouched. Previous bank kept as data/*.pre-2026.json.</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1480,32 +1480,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Your school is organizing a District level Community Fair. Which role would you naturally pick?</t>
+          <t>Your school is organizing a District-Level Community Fair. Which responsibility would you enjoy the most?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Diagnose community health issues and suggest remedies</t>
+          <t>Understanding the problem before suggesting a solution.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Build a tech device, software, or mechanical solution.</t>
+          <t>Finding smarter ways to make things work better.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Research local laws, policies, and present solutions to officials</t>
+          <t>Making sure every decision is fair and well considered.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Create posters, films, and branding for the fair</t>
+          <t>Communicating ideas that engage and inspire others.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Manage stall budgets, sponsorship money, and resource logistics.</t>
+          <t>Planning and coordinating everything to stay on track.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1519,34 +1519,34 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>A · Health &amp; Medical / Allied Health: Doctor, Nurse, Physiotherapist, Pharmacist
-B · Engineering &amp; Tech: Software Developer, Mechanical Engineer, Robotics Engineer
-C · Law &amp; Public Policy: Lawyer, Civil Servant (IAS), Policy Analyst, Mediator
-D · Arts, Media &amp; Design: Graphic Designer, Filmmaker, Journalist, Content Creator
-E · Business, Finance &amp; Mgmt: Chartered Accountant, Financial Analyst, Operations Mgr</t>
+          <t>A · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+B · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+C · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+D · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+E · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>A · S+I
+          <t>A · I+S
 B · R+I
-C · E+S+I
+C · S+E+C
 D · A+E
 E · C+E</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>A · S+3, I+2
+          <t>A · I+3, S+1
 B · R+3, I+2
-C · E+2, S+2, I+1
+C · S+2, E+2, C+1
 D · A+3, E+1
 E · C+3, E+2</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>finalised set 2026</t>
+          <t>behaviour-based rewrite</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr"/>
@@ -1559,803 +1559,787 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>If you could shadow an expert for a week during your summer break, who would you choose?</t>
+          <t>You can spend a week shadowing anyone at work. What would you most want to watch them do?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>A surgeon performing complex medical procedures or lab research.</t>
+          <t>Shape a rough idea into something people actually notice.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>An agronomist working on organic farming and crop genetics.</t>
+          <t>Keep a complicated operation running exactly to schedule.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>A corporate lawyer negotiating major international business deals.</t>
+          <t>Work out what is really going on before deciding anything.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>An animator or creative director producing a feature film.</t>
+          <t>Take something that half works and make it work properly.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A startup founder pitching to investors and building a company.</t>
+          <t>Weigh both sides of a difficult call and justify the decision.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>A · D — Arts, Media &amp; Design
+B · E — Business &amp; Marketing
+C · C — Health Science
+D · B — Information Technology
+E · F — Human &amp; Public Services</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>A · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+B · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+C · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+D · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+E · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>A · A+E
+B · C+E
+C · I+S
+D · R+I
+E · S+E+C</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>A · A+3, E+1
+B · C+3, E+2
+C · I+3, S+1
+D · R+3, I+2
+E · S+2, E+2, C+1</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Your town is setting up a new Model Village Project. Where would you want to be involved?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Designing how the whole thing should actually function.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Making sure the rules are fair to everyone affected.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Turning the plan into a schedule and a budget that holds.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Finding out what the village actually needs, and why.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Telling the story so people want to be part of it.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>A · A — Engineering &amp; Construction
+B · F — Human &amp; Public Services
+C · E — Business &amp; Marketing
+D · G — Science, Nature &amp; Agriculture
+E · D — Arts, Media &amp; Design</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>A · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+B · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+C · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+D · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+E · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>A · R+I
+B · S+E+C
+C · C+E
+D · I+S
+E · A+E</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>A · R+3, I+2
+B · S+2, E+2, C+1
+C · C+3, E+2
+D · I+3, S+1
+E · A+3, E+1</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="112" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>For your Class 10 exhibition you can lead one project. Which appeals to you most?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>One with many moving parts that must come together on time.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>One that looks and feels like nothing else on show.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>One where I build something and keep improving how it works.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>One that takes a contested issue and argues it properly.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>One where I test an idea and find out whether it holds up.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>A · E — Business &amp; Marketing
+B · D — Arts, Media &amp; Design
+C · B — Information Technology
+D · F — Human &amp; Public Services
+E · C — Health Science</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>A · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+B · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+C · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+D · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+E · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>A · C+E
+B · A+E
+C · R+I
+D · S+E+C
+E · I+S</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>A · C+3, E+2
+B · A+3, E+1
+C · R+3, I+2
+D · S+2, E+2, C+1
+E · I+3, S+1</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="112" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>You are given ₹10,000 for a student-led initiative. What would you put it into?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Something that fixes an unfairness people have stopped noticing.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Finding out why a problem keeps coming back.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Something people will still remember long after it ends.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Something that runs reliably every week without me.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Building a tool that saves everyone time.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>A · F — Human &amp; Public Services
+B · G — Science, Nature &amp; Agriculture
+C · D — Arts, Media &amp; Design
+D · E — Business &amp; Marketing
+E · B — Information Technology</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>A · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+B · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+C · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+D · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+E · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>A · S+E+C
+B · I+S
+C · A+E
+D · C+E
+E · R+I</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>A · S+2, E+2, C+1
+B · I+3, S+1
+C · A+3, E+1
+D · C+3, E+2
+E · R+3, I+2</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Which kind of story keeps you reading or watching the longest?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>How someone worked out the cause of something puzzling.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>How a huge undertaking was pulled off without falling apart.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>How a difficult decision was argued over and finally settled.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>How something was built to do what nobody thought possible.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>How an idea was made striking enough to change minds.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>A · G — Science, Nature &amp; Agriculture
+B · E — Business &amp; Marketing
+C · F — Human &amp; Public Services
+D · B — Information Technology
+E · D — Arts, Media &amp; Design</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>A · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+B · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+C · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+D · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+E · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>A · I+S
+B · C+E
+C · S+E+C
+D · R+I
+E · A+E</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>A · I+3, S+1
+B · C+3, E+2
+C · S+2, E+2, C+1
+D · R+3, I+2
+E · A+3, E+1</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="112" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Something goes badly wrong on a school trip. What do you find yourself doing?</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Fixing whatever has stopped working.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Getting a clear message out so nobody panics.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Working out what actually happened before anyone reacts.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Checking what we are responsible for and what the rules say.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Getting people, supplies and transport organised.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>A · A — Engineering &amp; Construction
+B · D — Arts, Media &amp; Design
+C · C — Health Science
+D · F — Human &amp; Public Services
+E · E — Business &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>A · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+B · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+C · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+D · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+E · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>A · R+I
+B · A+E
+C · I+S
+D · S+E+C
+E · C+E</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>A · R+3, I+2
+B · A+3, E+1
+C · I+3, S+1
+D · S+2, E+2, C+1
+E · C+3, E+2</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="112" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Which problem would you be proudest to have solved twenty years from now?</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>One where I changed how people see something.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>One where I left a system fairer than I found it.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>One where I made something work at a scale nobody had managed.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>One where I made a thing dramatically better than it was.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>One where I found the answer nobody else could find.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>A · D — Arts, Media &amp; Design
+B · F — Human &amp; Public Services
+C · E — Business &amp; Marketing
+D · B — Information Technology
+E · G — Science, Nature &amp; Agriculture</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>A · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+B · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+C · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+D · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+E · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>A · A+E
+B · S+E+C
+C · C+E
+D · R+I
+E · I+S</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>A · A+3, E+1
+B · S+2, E+2, C+1
+C · C+3, E+2
+D · R+3, I+2
+E · I+3, S+1</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="112" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Picture your work ten years from now. What would make it a good day?</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Everything I set up ran exactly as it should.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>I finally got a stubborn thing working.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>I made something I was proud to show people.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>I understood something that had been puzzling me for weeks.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>I argued a difficult case and got it right.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>A · E — Business &amp; Marketing
+B · A — Engineering &amp; Construction
+C · D — Arts, Media &amp; Design
+D · C — Health Science
+E · F — Human &amp; Public Services</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>A · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+B · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+C · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+D · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+E · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>A · C+E
+B · R+I
+C · A+E
+D · I+S
+E · S+E+C</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>A · C+3, E+2
+B · R+3, I+2
+C · A+3, E+1
+D · I+3, S+1
+E · S+2, E+2, C+1</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>You can add one extra subject next term, purely because you want to. What draws you?</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>One that trains you to reason through hard, contested questions.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>One that trains you to express an idea so that it lands.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>One that trains you to test a claim properly.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>One that trains you to run something from end to end.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>One that trains you to design and build.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>A · F — Human &amp; Public Services
+B · D — Arts, Media &amp; Design
+C · C — Health Science
+D · E — Business &amp; Marketing
+E · B — Information Technology</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>A · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+B · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+C · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+D · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+E · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>A · S+E+C
+B · A+E
+C · I+S
+D · C+E
+E · R+I</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>A · S+2, E+2, C+1
+B · A+3, E+1
+C · I+3, S+1
+D · C+3, E+2
+E · R+3, I+2</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="112" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>A company offers you a month with any one of its teams. Which do you ask for?</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>The team working out why the product keeps failing.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>The team rebuilding how the product actually works.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>The team keeping costs, stock and delivery on track.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>The team making sure it is safe and above board.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>The team deciding how it should look and feel.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · F — Human &amp; Public Services
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>A · Health &amp; Medical: Surgeon, Medical Researcher, Pathologist, Biomedical Scientist
-B · Agriculture &amp; Allied Sciences: Agronomist, Food Technologist, Environmental Scientist
-C · Law &amp; Commerce: Corporate Lawyer, Legal Consultant, Compliance Officer
-D · Arts &amp; Design: Animator, Game Designer, Fashion Designer, Art Director
-E · Business &amp; Entrepreneurship: Founder/CEO, Venture Capitalist, Product Manager</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+B · A — Engineering &amp; Construction
+C · E — Business &amp; Marketing
+D · F — Human &amp; Public Services
+E · D — Arts, Media &amp; Design</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>A · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+B · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+C · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+D · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor
+E · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>A · I+S
 B · R+I
-C · E+C
-D · A
-E · E+A</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>A · I+3, S+2
-B · R+3, I+2
-C · E+3, C+1
-D · A+3
-E · E+3, A+1</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="112" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Your town is setting up a new Model Village Project. Where would you make the biggest impact?</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Set up free health screening camps and wellness awareness.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Install modern irrigation, soil testing, and sustainable farming systems.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Construct smart bridges, renewable energy grids, and water systems.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Archive local history, write village stories, and preserve regional art.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Set up micro-finance banks and manage project budgets.</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · A — Engineering &amp; Construction
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>A · Health &amp; Allied Health: Community Health Specialist, Nutritionist, Public Health Mgr
-B · Agriculture &amp; Earth Sciences: Agricultural Engineer, Soil Scientist, Forester
-C · Engineering: Civil Engineer, Renewable Energy Specialist, Electrical Engineer
-D · Humanities &amp; Social Sciences: Historian, Anthropologist, Writer, Sociologist
-E · Finance &amp; Banking: Investment Banker, Microfinance Officer, Risk Analyst</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>A · S+I
-B · R+I
-C · R+I
-D · A+I
-E · C+E</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>A · S+3, I+1
-B · R+3, I+1
-C · R+3, I+2
-D · A+3, I+1
-E · C+3, E+2</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="112" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>For your Class 10 annual exhibition, which project topic would you be most eager to lead?</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Studying human anatomy, genetics, or disease prevention methods.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Building an automated solar tracker or smart home automation kit.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Debating constitutional rights, international relations, or student laws.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Displaying fine arts, photography, digital illustration, or set design.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Running a live stock-market simulation or business pitch deck.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · B — Information Technology
-C · F — Human &amp; Public Services
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>A · Medical &amp; Life Sciences: Physician, Geneticist, Microbiologist, Biotechnologist
-B · Engineering &amp; AI: AI Engineer, Electronics Engineer, Energy Systems Engineer
-C · Law, Politics &amp; Humanities: Criminal Lawyer, Diplomat, Political Analyst, Advocate
-D · Arts &amp; Creative Fields: Fine Artist, Photographer, Interior Designer, Illustrator
-E · Business &amp; Economics: Economist, Stock Broker, Marketing Manager, Business Analyst</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>A · I+S
-B · R+I
-C · E+S
-D · A
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+C · C+E
+D · S+E+C
+E · A+E</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>A · I+3, S+1
 B · R+3, I+2
-C · E+2, S+2
-D · A+3
-E · E+3, C+2</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="112" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>If you were given ₹10,000 to launch a student-led initiative, what would you fund?</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Rehabilitation equipment or mental health therapy sessions for peers.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Vertical hydroponic kits or organic seed beds for your school garden.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>A mobile coding lab or 3D printing setup for young inventors.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>A theatre production, podcast studio, or school newspaper magazine.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>An e-commerce store reselling handmade goods to earn profit.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>A · Allied Health &amp; Psychology: Clinical Psychologist, Occupational Therapist, Speech Therapist
-B · Agriculture &amp; Food Tech: Food Scientist, Horticulturist, Agricultural Businessman
-C · Tech &amp; Hardware: Hardware Engineer, Software Architect, Mechatronics Specialist
-D · Media, Journalism &amp; Arts: Journalist, Theatre Director, Radio Jockey, Copywriter
-E · Commerce &amp; Management: E-commerce Manager, Sales Director, Financial Planner</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>A · S+I
-B · R+I
-C · I+R
-D · A+E
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>A · S+3, I+1
-B · R+3, I+1
-C · I+3, R+2
-D · A+3, E+1
-E · E+3, C+2</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Which type of books, documentary channels, or podcasts capture your attention most?</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Medical breakthroughs, human brain mysteries, or emergency ER stories.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Wildlife conservation, forest ecosystems, and sustainable agriculture.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Space exploration, coding tutorials, and advanced robotics breakthroughs.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Crime thrillers, courtroom dramas, philosophy, and history podcasts.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Case studies on Fortune 500 companies, stock markets, and economics.</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · F — Human &amp; Public Services
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>A · Health &amp; Medical Sciences: Neuroscientist, Doctor, Radiologist, Anesthetist
-B · Environment &amp; Agriculture: Wildlife Biologist, Zoologist, Environmental Lawyer
-C · Science &amp; Technology: Astrophysicist, Data Scientist, Cybersecurity Analyst
-D · Law, Criminology &amp; Arts: Criminologist, Judge, Legal Journalist, Philosopher
-E · Business &amp; Finance: Business Consultant, Chartered Accountant (CA), CFA, Auditor</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>A · I+S
-B · I+R
-C · I+R
-D · A+S+E
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>A · I+3, S+1
-B · I+3, R+2
-C · I+3, R+2
-D · A+2, S+1, E+1
-E · E+3, C+2</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="112" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>During a crisis like a sudden epidemic in a school hostel, what is your instinct?</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Administer first aid, isolate the sick, and monitor physical symptoms.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Comfort anxious students, offer counseling, and boost team morale.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Study health guidelines, ensure legal protocols, and enforce safety rules.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Create clear infographics and announcements to keep everyone informed.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Audit food/water supplies, manage logistics, and secure needed funds.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · F — Human &amp; Public Services
-C · F — Human &amp; Public Services
-D · D — Arts, Media &amp; Design
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>A · Medical &amp; Emergency Health: Emergency Doctor, Epidemiologist, Paramedic
-B · Psychology &amp; Human Resources: Counselor, Psychologist, HR Manager, Social Worker
-C · Law &amp; Administration: Hospital Administrator, Compliance Officer, Civil Servant
-D · Design &amp; Communication: PR Specialist, Communications Mgr, Visual Designer
-E · Operations &amp; Supply Chain: Supply Chain Manager, Procurement Officer, Logistics Head</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>A · S+R
-B · S+A
-C · C+S
-D · A+E
-E · C+E</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>A · S+3, R+1
-B · S+3, A+1
-C · C+3, S+1
-D · A+3, E+1
-E · C+3, E+2</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Options B and C both map to Human &amp; Public Services, so two of the five choices give the same cluster signal and no Science/Agriculture option is offered. Left as supplied — scoring reads the per-option cluster tag, so it still works, but this item measures four families rather than five.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="112" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>What kind of practical problem would you feel most proud to solve in your career?</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Finding affordable cures or treatments for rare diseases.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Improving crop yields to tackle hunger without harming the soil.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Designing cleaner engines, faster computers, or automated systems.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Defending human rights, fighting injustice, or reforming laws.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Restructuring an struggling business to make it highly profitable.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · A — Engineering &amp; Construction
-D · F — Human &amp; Public Services
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>A · Medical Research: Pharmacologist, Oncologist, Genetic Researcher
-B · Agriculture Science: Soil Chemist, Plant Breeder, Agricultural Economist
-C · Core Engineering: Automobile Engineer, Computer Engineer, Chemical Engineer
-D · Legal &amp; Social Services: Human Rights Lawyer, Judge, NGO Leader, Policy Maker
-E · Corporate Management: Management Consultant, Chief Financial Officer (CFO), Strategist</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>A · I+S
-B · R+I
-C · R+I
-D · S+E
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>A · I+3, S+2
-B · R+3, I+2
-C · R+3, I+2
-D · S+3, E+2
-E · E+3, C+2</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Option E reads 'an struggling business' in the sheet. Left as supplied — a one-word typo fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="112" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>What kind of work environment sounds most appealing to you long-term?</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>A modern hospital, clinical lab, or emergency medical center.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Outdoor fields, greenhouses, research farms, or natural reserves.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>A modern tech hub, engineering workshop, or R&amp;D lab.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>A courtroom, law firm, media studio, or publishing house.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>A corporate boardroom, stock exchange floor, or financial firm.</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · F — Human &amp; Public Services
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>A · Health Sciences: Physician, Clinical Researcher, Surgeon, Medical Technologist
-B · Agriculture &amp; Earth: Forester, Environmental Consultant, Agricultural Scientist
-C · Engineering &amp; Tech: Software Engineer, Mechanical Engineer, Robotics Researcher
-D · Law &amp; Creative Arts: Advocate, Journalist, Editor, Creative Director
-E · Business &amp; Finance: Investment Banker, Equity Analyst, Corporate Executive</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>A · S+I
-B · R+I
-C · R+I
-D · A+E+S
-E · E+C</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>A · S+3, I+2
-B · R+3, I+1
-C · R+3, I+3
-D · A+2, E+2, S+1
-E · E+3, C+3</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Option D names both Law and Creative Arts, so a student picking it is ambiguous between clusters F and D. Left as supplied and tagged F; split the option if you want a clean signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="112" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>If you could take a specialized elective course next term, which would you pick?</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Human Physiology, Nutrition, and Clinical Health Basics.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Environmental Science, Crop Care, and Biotechnology.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Python Programming, Electronics, and Applied Mathematics.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>World History, Constitutional Law, and Creative Writing.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Financial Accounting, Entrepreneurship, and Business Marketing.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>A · C — Health Science
-B · G — Science, Nature &amp; Agriculture
-C · B — Information Technology
-D · F — Human &amp; Public Services
-E · E — Business &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>A · Health &amp; Allied Sciences: Dietitian, Physiotherapist, Sports Medicine Specialist
-B · Life Sciences &amp; Agriculture: Botanist, Biotechnologist, Agronomist
-C · Engineering &amp; Analytics: Data Analyst, Software Engineer, Electrical Engineer
-D · Law &amp; Humanities: Historian, Political Scientist, Journalist, Legal Scholar
-E · Commerce &amp; Management: Accountant, Marketing Strategist, Finance Manager</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>A · I+S
-B · I+R
-C · I+R
-D · A+S
-E · C+E</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>A · I+3, S+2
-B · I+3, R+2
-C · I+3, R+2
-D · A+3, S+1
-E · C+3, E+3</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>finalised set 2026</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="112" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>A company offers ten students a one-month paid internship. Which team would you ask to join?</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>The team working out why the product keeps failing.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>The team redesigning how the product looks and feels.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>The team training new users and answering their questions.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>The team tracking costs, stock and delivery schedules.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>The team testing whether the product is safe for people to use.</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>A · B — Information Technology
-B · D — Arts, Media &amp; Design
-C · F — Human &amp; Public Services
-D · E — Business &amp; Marketing
-E · C — Health Science</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>A · Research Scientist, AI Engineer, Software Engineer
-B · Architect, UX Designer, Graphic Designer
-C · Teacher, Psychologist, Lawyer
-D · Business Manager, Chartered Accountant, Operations Manager
-E · Clinical Research Associate, Pharmacologist, Quality &amp; Safety Officer</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>A · I+R
-B · A
-C · S+E
-D · C+E
-E · I+C</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>A · I+3, R+2
-B · A+3
-C · S+3, E+3
-D · C+3, E+3
-E · I+3, C+2</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>kept from live bank — sheet supplies only 10 interests questions</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
-        </is>
-      </c>
+C · C+3, E+2
+D · S+2, E+2, C+1
+E · A+3, E+1</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="112" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -2365,80 +2349,76 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Your school is starting a student-run magazine and website. Which role would you take?</t>
+          <t>Your school starts a student magazine and website. Which job do you take?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Research the stories, check the facts, and build the website.</t>
+          <t>Deciding how it looks and how each story gets told.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Design the layout, illustrations, photographs, and cover art.</t>
+          <t>Digging out the facts and checking that they hold up.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Interview people, build the writing team, and reply to readers.</t>
+          <t>Building the site and keeping it fast and working.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Handle advertising, budgets, and the publishing schedule.</t>
+          <t>Running the schedule, the budget and the ad slots.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Cover the health, fitness and wellbeing section for students.</t>
+          <t>Deciding what we should and should not publish.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>A · B — Information Technology
-B · D — Arts, Media &amp; Design
-C · F — Human &amp; Public Services
+          <t>A · D — Arts, Media &amp; Design
+B · C — Health Science
+C · B — Information Technology
 D · E — Business &amp; Marketing
-E · C — Health Science</t>
+E · F — Human &amp; Public Services</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>A · Software Engineer, Data Analyst, Research Scientist
-B · Graphic Designer, Animator, Product Designer
-C · Teacher, Lawyer, Psychologist
-D · Business Manager, Financial Analyst, Digital Marketer
-E · Health Journalist, Public Health Educator, Medical Writer</t>
+          <t>A · Media, Design, Mass Communication, Digital Marketing: Graphic Designer, Animator, Journalist, Architect, Content Creator
+B · Health &amp; Medical Sciences, Psychology, Life Sciences &amp; Research: Doctor, Research Scientist, Psychologist, Pharmacist
+C · Engineering &amp; Technology, Computer Science, Robotics: Software Engineer, Mechanical Engineer, Robotics Engineer, AI Engineer, Civil Engineer
+D · Business, Commerce, Management, Entrepreneurship: Operations Manager, Chartered Accountant, Project Manager, Business Manager, Financial Analyst
+E · Law, Public Policy &amp; Governance, Civil Services: Lawyer, IAS Officer, Social Worker, Counsellor</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>A · I+R
-B · A
-C · S+E
+          <t>A · A+E
+B · I+S
+C · R+I
 D · C+E
-E · S+A+I</t>
+E · S+E+C</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>A · I+3, R+2
-B · A+3
-C · S+3, E+2
+          <t>A · A+3, E+1
+B · I+3, S+1
+C · R+3, I+2
 D · C+3, E+2
-E · S+2, A+2, I+1</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>kept from live bank — sheet supplies only 10 interests questions</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>The sheet supplies 10 interests questions; the old count is 12. Q11 and Q12 therefore keep the questions already live in the bank, marked 'kept from live bank' in the Source column. Send two more in the sheet's 5-family format and they will replace those slots.</t>
-        </is>
-      </c>
+E · S+2, E+2, C+1</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>behaviour-based rewrite</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2584,7 +2564,7 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2657,7 +2637,7 @@
           <t>All researchers are science teachers.</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2730,7 +2710,7 @@
           <t>Tractor</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -2765,7 +2745,7 @@
           <t>finalised set 2026 item 13</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>Cluster tag follows the correct answer (Tractor) rather than the skill being tested. Left as supplied.</t>
         </is>
@@ -2807,7 +2787,7 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2817,7 +2797,7 @@
           <t>Data Interpretation</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -2842,7 +2822,7 @@
           <t>finalised set 2026 item 14</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>Cluster tag (Health &amp; Life Sciences) does not follow from an electricity-usage item. Left as supplied.</t>
         </is>
@@ -2884,7 +2864,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2894,7 +2874,7 @@
           <t>Spatial Reasoning</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -2919,7 +2899,7 @@
           <t>finalised set 2026 item 15</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>Marked '(visual item)' in the sheet — artwork is mandatory. Cluster tag does not follow from paper folding.</t>
         </is>
@@ -2961,7 +2941,7 @@
           <t>Policy</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3034,7 +3014,7 @@
           <t>8714</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3069,7 +3049,7 @@
           <t>finalised set 2026 item 18</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O8" s="10" t="inlineStr">
         <is>
           <t>DEFECT — the two keys contradict each other. TECH=3142 gives T=3; ARTS=5678 gives T=7. The marked answer 6571 assumes T=7. Left exactly as supplied. Fix by changing one key word (ARTS=5637 makes T=3 throughout and RATE=6531), or state that each word uses its own key.</t>
         </is>
@@ -3111,7 +3091,7 @@
           <t>11 Lines</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3121,7 +3101,7 @@
           <t>Abstract Reasoning</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -3146,7 +3126,7 @@
           <t>finalised set 2026 item 19</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="10" t="inlineStr">
         <is>
           <t>DEFECT — the answer needs two rules at once (count +2, sides +1), and circle-to-triangle breaks the sides rule, so option D is arguable. Left as supplied. Starting the series at a triangle would resolve it.</t>
         </is>
@@ -3188,7 +3168,7 @@
           <t>e</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -3223,7 +3203,7 @@
           <t>finalised set 2026 item 14 (second block)</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O10" s="10" t="inlineStr">
         <is>
           <t>DEFECT — the stem lists 456789 twice, so BOTH 456798 and 456879 are unique and the item has two correct answers. Option E is also a stray letter 'e'. Left exactly as supplied. Fix by listing 456789 three times and giving E an 'All are the same' distractor.</t>
         </is>
@@ -3265,7 +3245,7 @@
           <t>Cannot say</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -3275,7 +3255,7 @@
           <t>Mechanical Reasoning</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -3452,7 +3432,7 @@
           <t>finalised set 2026</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Option B reads 'Clearest, idea most reliable approach' — a stray word. Left as supplied.</t>
         </is>
@@ -3766,7 +3746,7 @@
           <t>finalised set 2026</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Facet recorded as Initiative rather than the old set's Confidence: this scenario is about starting a conversation, which keeps it distinct from Q29.</t>
         </is>
@@ -3894,7 +3874,7 @@
           <t>finalised set 2026</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>Facets are the reverse of the old set here: old Q30 measured Empathy, old Q31 Cooperation. Mapped to match the sheet's scenarios.</t>
         </is>
@@ -3960,7 +3940,7 @@
           <t>finalised set 2026</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>See Q30 — facets swapped relative to the old set.</t>
         </is>
@@ -4154,12 +4134,12 @@
     </row>
     <row r="14"/>
     <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
         </is>
@@ -4422,7 +4402,7 @@
           <t>A · Analytical+3, Execution+1
 B · Analytical+3, Learning+1
 C · Communication+3, Leadership+1
-D · Leadership+3, Execution+1
+D · Leadership+3, Adaptability+1
 E · Creative+3, Communication+1</t>
         </is>
       </c>
@@ -4773,7 +4753,7 @@
         <is>
           <t>A · Analytical+3, Learning+2
 B · Execution+3, Analytical+2
-C · Learning+3, Analytical+1
+C · Learning+3, Adaptability+1
 D · Communication+3, Analytical+1
 E · Creative+3, Leadership+1</t>
         </is>
@@ -4950,7 +4930,7 @@
           <t>A · Execution+3, Analytical+1
 B · Execution+3, Relationship+2
 C · Analytical+3, Execution+1
-D · Execution+3, Leadership+1
+D · Execution+3, Adaptability+1
 E · Relationship+3, Communication+2</t>
         </is>
       </c>
@@ -4976,12 +4956,12 @@
     </row>
     <row r="10"/>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
         </is>
@@ -6658,12 +6638,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Scoring model. Every option on every item is a healthy response naming a DIFFERENT EQ domain, so there is no weak answer to score against and no defensible EQ level. The engine therefore counts which domain the student reaches for and reports a PROFILE; the EQ percentage is left null rather than publishing an out-of-100 figure off one observation per domain. This replaces the live bank's graded 3/2/2/1 model.</t>
         </is>

--- a/docs/finalised set 2026.xlsx
+++ b/docs/finalised set 2026.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>VARK — Visual, Auditory, Reading/Writing, Kinesthetic, Multimodal</t>
+          <t>VARK — Visual, Auditory, Reading/Writing, Kinesthetic, Multimodal (a specific two-mode strategy, not 'do everything')</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
+          <t>Each item is one scenario; the five options are different ways of responding to it, so the section measures working style rather than subject preference — the previous version varied the subject and duplicated the Interests scale. Every option carries a cost (covering for a teammate means resenting it; arguing your case means annoying the teacher; asking for help means looking clueless), so there is no flattering answer to pick without thinking. Scored on the eight domains the career map already uses, and rolled up to four reporting groups: Delivering, Persuading, Connecting, Reasoning.</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
+          <t>Every item now offers five real positions with a downside each — the bold idea may not work, the safe one is dull, asking others means depending on them, finishing early means handing in less. The old 'None of these' opt-out is gone, which removes 13 dead options and the risk of a student answering the whole section with it. An option carrying no weights is NOT an abstention: keeping to yourself is real evidence about extraversion, so it stays in the denominator and correctly pulls the trait down.</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>dropped: ₹10,000 social impact project</t>
+          <t>dropped: all 8 supplied items</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Cut only because the count caps at 8.</t>
+          <t>Replaced wholesale: they varied by subject, not working style, so the section duplicated the Interests scale rather than adding a second signal.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -1225,17 +1225,17 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Learning styles</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>dropped: long-term problem giving deepest satisfaction</t>
+          <t>dropped: item 9 — 'At home, I am easily distracted by:'</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Cut only because the count caps at 8.</t>
+          <t>Not a VARK item — it is a distraction inventory, and option C (phone texts) has nothing to do with Reading/Writing. Would have been cut on quality even if the count allowed it.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1247,17 +1247,17 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Learning styles</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>dropped: one elective course for next term</t>
+          <t>dropped: items 1, 3, 4, 5, 6, 8</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Cut only because the count caps at 8; overlaps interests Q10.</t>
+          <t>Valid items, cut only because the count caps at 4.</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1269,17 +1269,17 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Emotional intelligence</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>dropped: 48 hours to present a final major project</t>
+          <t>dropped: items 6-10 — praise for shared work; unexpected criticism; little time left; new student; after a hard task</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Cut only because the count caps at 8.</t>
+          <t>Valid items, cut only because the count caps at 5. Items 1-5 were kept because they line up one-to-one with the live bank's Q56-Q60 dimensions.</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1291,86 +1291,20 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Learning styles</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>dropped: item 9 — 'At home, I am easily distracted by:'</t>
+          <t>Live questions replaced</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Not a VARK item — it is a distraction inventory, and option C (phone texts) has nothing to do with Reading/Writing. Would have been cut on quality even if the count allowed it.</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Over count</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Learning styles</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>dropped: items 1, 3, 4, 5, 6, 8</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Valid items, cut only because the count caps at 4.</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Over count</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Emotional intelligence</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>dropped: items 6-10 — praise for shared work; unexpected criticism; little time left; new student; after a hard task</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Valid items, cut only because the count caps at 5. Items 1-5 were kept because they line up one-to-one with the live bank's Q56-Q60 dimensions.</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Over count</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Live questions replaced</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
           <t>scripts/import_finalised_set_2026.py writes this set into project/data/*.json (classes 9-10, Set 1). All other life stages and sets are untouched. Previous bank kept as data/*.pre-2026.json.</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -1485,7 +1419,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Understanding the problem before suggesting a solution.</t>
+          <t>Understand the problem before fixing it.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1495,17 +1429,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Making sure every decision is fair and well considered.</t>
+          <t>Make sure the decision is a fair one.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Communicating ideas that engage and inspire others.</t>
+          <t>Get people interested in the idea.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Planning and coordinating everything to stay on track.</t>
+          <t>Keep the whole thing on schedule.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1564,27 +1498,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Shape a rough idea into something people actually notice.</t>
+          <t>Turn a rough idea into something noticed.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Keep a complicated operation running exactly to schedule.</t>
+          <t>Keep a messy operation on schedule.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Work out what is really going on before deciding anything.</t>
+          <t>Work out what is really going on.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Take something that half works and make it work properly.</t>
+          <t>Make something half-working work.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Weigh both sides of a difficult call and justify the decision.</t>
+          <t>Weigh a hard call and justify it.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1643,27 +1577,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Designing how the whole thing should actually function.</t>
+          <t>Design how the whole thing works.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Making sure the rules are fair to everyone affected.</t>
+          <t>Set rules that are fair to everyone.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Turning the plan into a schedule and a budget that holds.</t>
+          <t>Turn the plan into a budget that holds.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Finding out what the village actually needs, and why.</t>
+          <t>Find out what is actually needed, and why.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Telling the story so people want to be part of it.</t>
+          <t>Tell it so people want to join in.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1722,27 +1656,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>One with many moving parts that must come together on time.</t>
+          <t>Many moving parts, all due at once.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>One that looks and feels like nothing else on show.</t>
+          <t>Looks like nothing else on show.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>One where I build something and keep improving how it works.</t>
+          <t>Build it, then keep improving it.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>One that takes a contested issue and argues it properly.</t>
+          <t>Take a contested issue and argue it.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>One where I test an idea and find out whether it holds up.</t>
+          <t>Test an idea and see if it holds up.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1801,27 +1735,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Something that fixes an unfairness people have stopped noticing.</t>
+          <t>Fix an unfairness people ignore.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Finding out why a problem keeps coming back.</t>
+          <t>Find out why it keeps coming back.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Something people will still remember long after it ends.</t>
+          <t>Something people remember afterwards.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Something that runs reliably every week without me.</t>
+          <t>Runs every week without me.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Building a tool that saves everyone time.</t>
+          <t>Build a tool that saves time.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1880,27 +1814,27 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>How someone worked out the cause of something puzzling.</t>
+          <t>How someone found the cause.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>How a huge undertaking was pulled off without falling apart.</t>
+          <t>How something huge held together.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>How a difficult decision was argued over and finally settled.</t>
+          <t>How a hard decision got settled.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>How something was built to do what nobody thought possible.</t>
+          <t>How something impossible got built.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>How an idea was made striking enough to change minds.</t>
+          <t>How an idea changed minds.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1959,27 +1893,27 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Fixing whatever has stopped working.</t>
+          <t>Fix whatever has stopped working.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Getting a clear message out so nobody panics.</t>
+          <t>Get a clear message out fast.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Working out what actually happened before anyone reacts.</t>
+          <t>Work out what actually happened.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Checking what we are responsible for and what the rules say.</t>
+          <t>Check what the rules actually say.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Getting people, supplies and transport organised.</t>
+          <t>Get people and supplies organised.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2038,27 +1972,27 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>One where I changed how people see something.</t>
+          <t>I changed how people see something.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>One where I left a system fairer than I found it.</t>
+          <t>I left a system fairer than I found it.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>One where I made something work at a scale nobody had managed.</t>
+          <t>I made it work at a huge scale.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>One where I made a thing dramatically better than it was.</t>
+          <t>I made a thing far better.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>One where I found the answer nobody else could find.</t>
+          <t>I found the answer nobody else could.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -2117,27 +2051,27 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Everything I set up ran exactly as it should.</t>
+          <t>Everything I set up just worked.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>I finally got a stubborn thing working.</t>
+          <t>I got a stubborn thing working.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>I made something I was proud to show people.</t>
+          <t>I made something worth showing.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>I understood something that had been puzzling me for weeks.</t>
+          <t>I understood something long puzzling.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>I argued a difficult case and got it right.</t>
+          <t>I argued a hard case and got it right.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2196,27 +2130,27 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>One that trains you to reason through hard, contested questions.</t>
+          <t>Reasoning through contested questions.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>One that trains you to express an idea so that it lands.</t>
+          <t>Expressing an idea so it lands.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>One that trains you to test a claim properly.</t>
+          <t>Testing a claim properly.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>One that trains you to run something from end to end.</t>
+          <t>Running something end to end.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>One that trains you to design and build.</t>
+          <t>Designing and building things.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2275,27 +2209,27 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The team working out why the product keeps failing.</t>
+          <t>Working out why it keeps failing.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>The team rebuilding how the product actually works.</t>
+          <t>Rebuilding how the product works.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>The team keeping costs, stock and delivery on track.</t>
+          <t>Keeping costs and delivery on track.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>The team making sure it is safe and above board.</t>
+          <t>Making sure it is safe and legal.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>The team deciding how it should look and feel.</t>
+          <t>Deciding how it looks and feels.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2354,27 +2288,27 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Deciding how it looks and how each story gets told.</t>
+          <t>Deciding how each story gets told.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Digging out the facts and checking that they hold up.</t>
+          <t>Digging out facts and checking them.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Building the site and keeping it fast and working.</t>
+          <t>Building the site and keeping it fast.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Running the schedule, the budget and the ad slots.</t>
+          <t>Running the schedule and the budget.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Deciding what we should and should not publish.</t>
+          <t>Deciding what we should not publish.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -3380,32 +3314,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>One weekend to prep a project on an unfamiliar topic; by Saturday evening still have several directions. What would you most likely do?</t>
+          <t>One weekend to prepare a project on a topic you have never touched. By Saturday night you still have several directions. What do you do?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Most unusual idea, even if risky</t>
+          <t>Chase the riskiest idea and see.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Clearest, idea most reliable approach</t>
+          <t>Take the safest one and finish.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Discuss options with classmates</t>
+          <t>Ask classmates which to pick.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Combine ideas from different sources</t>
+          <t>Blend the best bits of each.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Stick with my first instinct.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -3423,8 +3357,8 @@
           <t>A · O+3
 B · C+3
 C · E+2, A+2
-D · O+3, C+1
-E · not scored</t>
+D · O+2, C+1
+E · S+2, C+1</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -3432,11 +3366,7 @@
           <t>finalised set 2026</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>Option B reads 'Clearest, idea most reliable approach' — a stray word. Left as supplied.</t>
-        </is>
-      </c>
+      <c r="L2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="96" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3446,32 +3376,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>School exhibition, must choose one project. Which would you most enjoy building?</t>
+          <t>Your school exhibition lets you build anything. Which do you go for?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Challenges conventional thinking</t>
+          <t>Something nobody would expect.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Carefully planned, tested project</t>
+          <t>Something I have tested and trust.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Interactive, participatory project</t>
+          <t>Something visitors join in with.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Visually creative project</t>
+          <t>Something that simply looks striking.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Whatever I can finish in time.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -3489,8 +3419,8 @@
           <t>A · O+3
 B · C+3
 C · E+3, A+2
-D · O+3, A+1
-E · not scored</t>
+D · O+2, A+1
+E · C+2, S+1</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -3508,32 +3438,32 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Assignment due in two weeks, but an unexpected event cuts your study days. What would you most likely do?</t>
+          <t>An assignment is due in two weeks and something unexpected takes your study days away.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Adjust schedule, follow revised plan</t>
+          <t>Redo the schedule and follow it.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Rethink best approach before restarting</t>
+          <t>Rethink the whole approach first.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Work longer hours to catch up</t>
+          <t>Work late and push through.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Study with others to stay on track</t>
+          <t>Work with others to keep up.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Hand in less, but on time.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -3552,7 +3482,7 @@
 B · O+2, C+1
 C · C+2, S+1
 D · E+2, A+2
-E · not scored</t>
+E · S+2, C+1</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3570,32 +3500,32 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>After an hour studying a hard chapter, still don't understand it. What usually happens next?</t>
+          <t>An hour into a hard chapter and it still will not go in. What happens next?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Try a different study method</t>
+          <t>Try a completely different method.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Take a break, return later</t>
+          <t>Leave it and come back later.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Ask someone to explain</t>
+          <t>Get someone to explain it.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Keep practicing despite unclear theory</t>
+          <t>Keep drilling it until it sticks.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Move on and lose those marks.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -3614,7 +3544,7 @@
 B · S+2
 C · E+2, A+1
 D · C+3
-E · not scored</t>
+E · S+1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3632,32 +3562,32 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Halfway through organizing a school event, several problems appear at once. Which role do you take?</t>
+          <t>Halfway through organising a school event, several things go wrong at once.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Keep everything organized</t>
+          <t>Keep the lists and the order.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Suggest new ideas/solutions</t>
+          <t>Throw new solutions at it.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Keep everyone coordinated &amp; motivated</t>
+          <t>Keep people calm and moving.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Tackle the most urgent problem first</t>
+          <t>Fix the worst thing first.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Do my own bit properly and stop.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -3676,7 +3606,7 @@
 B · O+3
 C · E+3, A+2
 D · S+3, C+1
-E · not scored</t>
+E · C+2</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -3694,32 +3624,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Arrive early for a workshop; most students already talking. What would you most likely do?</t>
+          <t>You arrive early at a workshop and everyone is already talking.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Join conversation naturally</t>
+          <t>Walk over and join in.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Observe before joining</t>
+          <t>Watch for a while first.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Talk if shared interests noticed</t>
+          <t>Wait for a topic I know.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Wait to be included</t>
+          <t>Keep to myself until it starts.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Ask someone a direct question.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -3738,7 +3668,7 @@
 B · C+1, O+1
 C · E+2, A+1
 D · not scored
-E · not scored</t>
+E · E+2, C+1</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -3748,7 +3678,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Facet recorded as Initiative rather than the old set's Confidence: this scenario is about starting a conversation, which keeps it distinct from Q29.</t>
+          <t>Facet is Initiative rather than Confidence: this is about starting a conversation, which keeps it distinct from Q29.</t>
         </is>
       </c>
     </row>
@@ -3760,32 +3690,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Joined a new class for a semester. By end of first week, what's most likely true?</t>
+          <t>You joined a new class this term. By the end of week one, what is true?</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Already introduced myself to many</t>
+          <t>I have met most of the class.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Spoke mainly when needed</t>
+          <t>I have spoken when needed.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Connected with a few similar people</t>
+          <t>I have found two or three people.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Focused on settling in first</t>
+          <t>I have kept my head down.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>I have let people come to me.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -3804,7 +3734,7 @@
 B · C+2
 C · E+2, A+2
 D · C+2
-E · not scored</t>
+E · S+1</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -3822,32 +3752,32 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>During a team activity, two members disagree on how to complete work. What would you naturally do?</t>
+          <t>Two people in your team disagree about how to do the work.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Help both sides understand each other</t>
+          <t>Get them to hear each other.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Combine strongest parts of both ideas</t>
+          <t>Take the best of both ideas.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Let group decide, focus on own task</t>
+          <t>Let the group vote and move on.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Choose most practical option</t>
+          <t>Pick whichever is more practical.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Stay out of it entirely.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -3866,7 +3796,7 @@
 B · A+2, O+2
 C · C+2
 D · C+2, S+1
-E · not scored</t>
+E · S+1</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -3876,7 +3806,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Facets are the reverse of the old set here: old Q30 measured Empathy, old Q31 Cooperation. Mapped to match the sheet's scenarios.</t>
+          <t>Facets are the reverse of the old set: old Q30 measured Empathy, old Q31 Cooperation. Mapped to match these scenarios.</t>
         </is>
       </c>
     </row>
@@ -3888,32 +3818,32 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A teammate is falling behind, deadline approaching. What feels most natural?</t>
+          <t>A teammate is falling behind and the deadline is close.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Support them, encourage their own effort</t>
+          <t>Back them, but let them do it.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Adjust plan for fair contribution</t>
+          <t>Redivide the work fairly.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Finish part of task to help team</t>
+          <t>Take some of their load.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Focus on own responsibilities first</t>
+          <t>Finish mine and leave theirs.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Tell the teacher about it.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -3932,7 +3862,7 @@
 B · A+2, C+2
 C · A+2, C+2
 D · C+2
-E · not scored</t>
+E · C+1, S+1</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -3954,32 +3884,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Result is much lower than expected after working hard. What would you most likely do next?</t>
+          <t>You worked hard and the result came back far lower than you expected.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Review mistakes, adjust approach</t>
+          <t>Go through my mistakes.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Ask for feedback</t>
+          <t>Ask where I went wrong.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Take a short break, restart</t>
+          <t>Step away, then restart.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Accept result, keep working steadily</t>
+          <t>Accept it and carry on.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Let it bother me for a while.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -4016,32 +3946,32 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Just before presenting, realize an important part is missing. First reaction?</t>
+          <t>Minutes before presenting, you realise an important part is missing.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Quickly find another way to explain</t>
+          <t>Explain it another way, fast.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Pause, understand, then continue</t>
+          <t>Pause, think, then continue.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Ask someone nearby for help</t>
+          <t>Ask someone next to me.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Continue and adapt as needed</t>
+          <t>Carry on and improvise.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Say it is missing and move on.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -4060,7 +3990,7 @@
 B · S+3, C+2
 C · A+2, E+2, S+1
 D · S+2, C+1
-E · not scored</t>
+E · S+2</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -4078,32 +4008,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Four internship offers with same salary/growth. Which would you most enjoy?</t>
+          <t>Four internships, same pay, same prospects. Which do you take?</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Learn something completely new</t>
+          <t>One where I learn something new.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Create original ideas/designs/solutions</t>
+          <t>One where I make original things.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Work closely with people, help teams</t>
+          <t>One where I work with people.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Improve systems, boost efficiency</t>
+          <t>One where I make systems work.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>One with clear hours and rules.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -4122,7 +4052,7 @@
 B · O+3, E+1
 C · E+3, A+3
 D · C+3, S+1
-E · not scored</t>
+E · C+2, S+2</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -4141,7 +4071,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Option E is 'None of these' on all 12 items and scores nothing. The engine treats it as an ABSTENTION (abstainIndex = 4): the item drops out of that student's denominator instead of deflating every trait, and if more than half the items are abstained the Big Five profile is suppressed rather than published as a near-zero. Note also that the options are written as shorthand rather than full sentences — they read as internal notes and are worth expanding before a Class 9-10 student sees them.</t>
+          <t>Every item now offers five real positions with a downside each — the bold idea may not work, the safe one is dull, asking others means depending on them, finishing early means handing in less. The old 'None of these' opt-out is gone, which removes 13 dead options and the risk of a student answering the whole section with it. An option carrying no weights is NOT an abstention: keeping to yourself is real evidence about extraversion, so it stays in the denominator and correctly pulls the trait down.</t>
         </is>
       </c>
     </row>
@@ -4171,11 +4101,11 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4186,7 +4116,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4216,17 +4146,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Strength Domain(s) Measured (sheet)</t>
+          <t>Domains Measured</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Client Domain (per option)</t>
+          <t>Domain (per option)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Strength Domain — engine (derived)</t>
+          <t>Report Group (per option)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -4246,7 +4176,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Source (per option)</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -4258,611 +4188,583 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Your school is leading a District Youth Summit. Which track do you choose to direct?</t>
+          <t>Your group presents next week and one member still hasn't done anything. What do you actually do?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Smart Tech &amp; AI: Coding automation tools or robotics exhibits.</t>
+          <t>Tell them straight, even if it gets awkward.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Health &amp; Bio-Care: Demonstrating medical diagnostic tools &amp; first-aid.</t>
+          <t>Check whether the plan was ever realistic.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Eco-Agri Solutions: Setting up hydroponic farming &amp; soil tests.</t>
+          <t>Ask them privately, and lose a day over it.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Law &amp; Public Policy: Hosting mock parliament &amp; debating policies.</t>
+          <t>Do their part myself and say nothing.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Media &amp; Design: Producing the summit's films, posters and live coverage.</t>
+          <t>Cut their section out of the presentation.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Technical, Medical, Environmental, Legal/Policy</t>
+          <t>Leadership, Analytical, Relationship, Execution, Creative</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>A · Technical
-B · Medical
-C · Environmental
-D · Legal/Policy
-E · Creative/Media</t>
+          <t>A · Leadership
+B · Analytical
+C · Relationship
+D · Execution
+E · Creative</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
+          <t>A · Persuading
+B · Reasoning
+C · Connecting
+D · Delivering
+E · Reasoning</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>A · Leadership+3, Communication+1
+B · Analytical+3, Learning+1
+C · Relationship+3, Adaptability+1
+D · Execution+3, Analytical+1
+E · Creative+3, Adaptability+1</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Management, Education, Research, Operations</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager, Teacher, Research Scientist, Operations Manager</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q36</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>You are handed a task nobody has explained, with no instructions. How do you start?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Read up first, even if it eats my time.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Start now and get some of it wrong.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Keep asking until someone explains it.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Try something, switch when it fails.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Map it out before touching anything.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Learning, Execution, Communication, Adaptability, Analytical</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>A · Learning
+B · Execution
+C · Communication
+D · Adaptability
+E · Analytical</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>A · Reasoning
+B · Delivering
+C · Persuading
+D · Connecting
+E · Reasoning</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>A · Learning+3, Analytical+1
+B · Execution+3, Adaptability+1
+C · Communication+3, Relationship+1
+D · Adaptability+3, Creative+1
+E · Analytical+3, Execution+1</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Research, Technology, Consulting, Operations</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Research Scientist, Software Engineer, Consultant, Data Analyst</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Your school is raising money for a new library and you can pick your role.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Try something new that might flop.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Stand up and do the asking.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Keep volunteers going when they lose interest.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Decide, and carry the blame if it fails.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Copy what worked at other schools.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Creative, Communication, Relationship, Leadership, Learning</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>A · Creative
+B · Communication
+C · Relationship
+D · Leadership
+E · Learning</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>A · Reasoning
+B · Persuading
+C · Connecting
+D · Persuading
+E · Reasoning</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>A · Creative+3, Adaptability+1
+B · Communication+3, Leadership+1
+C · Relationship+3, Execution+1
+D · Leadership+3, Execution+1
+E · Learning+3, Analytical+1</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Marketing, Public Service, Education, Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Digital Marketer, Social Worker, Teacher, Entrepreneur</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q38</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A teacher rejects the idea you spent a week on. What is your honest next move?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Drop it and start something else.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Rebuild it to the brief, duller but safe.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Keep the idea, change how I sell it.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Find the exact part that failed.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Argue back, and risk annoying them.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Adaptability, Execution, Creative, Analytical, Leadership</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>A · Adaptability
+B · Execution
+C · Creative
+D · Analytical
+E · Leadership</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>A · Connecting
+B · Delivering
+C · Reasoning
+D · Reasoning
+E · Persuading</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>A · Adaptability+3, Creative+1
+B · Execution+3, Analytical+1
+C · Creative+3, Communication+1
+D · Analytical+3, Learning+1
+E · Leadership+3, Communication+1</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Design, Engineering, Law, Research</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Product Designer, Engineer, Lawyer, Research Scientist</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="112" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q39</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Younger students are joining and someone has to look after them. What appeals to you?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Run the sessions and do the talking.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sit with the one who is struggling.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Work out why they struggle first.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Get good at it before I start.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Turn up and work it out as I go.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Communication, Relationship, Analytical, Learning, Adaptability</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>A · Communication
+B · Relationship
+C · Analytical
+D · Learning
+E · Adaptability</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>A · Persuading
+B · Connecting
+C · Reasoning
+D · Reasoning
+E · Connecting</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>A · Communication+3, Leadership+1
+B · Relationship+3, Adaptability+1
+C · Analytical+3, Learning+1
+D · Learning+3, Execution+1
+E · Adaptability+3, Relationship+1</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Education, Psychology, Human Resources, Public Service</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Teacher, Psychologist, HR Manager, Counsellor</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q40</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Two weeks into a plan, the situation changes completely. What do you do?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Check how everyone is taking it.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Decide fast, without full agreement.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Use it to build something better.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Adjust as we go, no re-planning.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Stop until I understand what changed.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Relationship, Leadership, Creative, Adaptability, Learning</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>A · Relationship
+B · Leadership
+C · Creative
+D · Adaptability
+E · Learning</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>A · Connecting
+B · Persuading
+C · Reasoning
+D · Connecting
+E · Reasoning</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>A · Relationship+3, Communication+1
+B · Leadership+3, Execution+1
+C · Creative+3, Adaptability+1
+D · Adaptability+3, Execution+1
+E · Learning+3, Analytical+1</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Management, Operations, Design, Consulting</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Business Manager, Operations Manager, Creative Director, Consultant</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>working-style rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="112" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q41</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>You are asked to check someone's work before it is handed in. How do you do it?</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>List every single thing that is wrong.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Fix what I can so it goes in on time.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Flag the big things, ignore the rest.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Tell them honestly, even if it stings.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Suggest a different angle entirely.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Analytical, Execution, Adaptability, Communication, Creative</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
           <t>A · Analytical
-B · Relationship
-C · Execution
+B · Execution
+C · Adaptability
 D · Communication
 E · Creative</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>A · Reasoning
+B · Delivering
+C · Connecting
+D · Persuading
+E · Reasoning</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>A · Analytical+3, Execution+1
-B · Relationship+3, Analytical+1
-C · Execution+3, Learning+1
+B · Execution+3, Analytical+1
+C · Adaptability+3, Analytical+1
 D · Communication+3, Leadership+1
-E · Creative+3, Communication+1</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>STEM &amp; AI, Health &amp; Life Sciences, Agriculture &amp; Earth Sciences, Law &amp; Public Service</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer, Medical Doctor, Agricultural Engineer, Lawyer / IAS Officer</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="112" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Q36</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>A local neighborhood faces severe water logging and waste management issues. What is your first step?</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Build a smart sensor prototype to monitor drainage flow.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Conduct water purity &amp; health risk testing for residents.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Draft a legal petition &amp; campaign to municipal authorities.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Launch a local micro-funded recycling business model.</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Run an awareness drive with posters, films and street theatre.</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Engineering, Clinical/Bio-Health, Advocacy/Legal, Financial/Business</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>A · Engineering
-B · Clinical/Bio-Health
-C · Advocacy/Legal
-D · Financial/Business
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Analytical
-C · Communication
-D · Leadership
-E · Creative</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Execution+1
-B · Analytical+3, Learning+1
-C · Communication+3, Leadership+1
-D · Leadership+3, Adaptability+1
-E · Creative+3, Communication+1</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Core Engineering, Public Health, Law &amp; Governance, Commerce &amp; Business</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Civil Engineer, Epidemiologist, Environmental Lawyer, Business Manager</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="112" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Q37</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Your school gets funding for one new modern learning facility. Which proposal do you champion?</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Computer &amp; Tech R&amp;D Lab: 3D printers, coding kits, &amp; server gear.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Biology &amp; Medical Lab: Advanced microscopes &amp; human anatomy models.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Greenhouse &amp; Soil Lab: Eco-gardening, crop genetics, &amp; bio-fertilizers.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Debate &amp; Legal Clinic: Courtroom setup for legal &amp; civic studies.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Media &amp; Design Studio: cameras, editing suites and a design lab.</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Analytical, Diagnostic, Ecological, Civic/Communicative</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Diagnostic
-C · Ecological
-D · Civic/Communicative
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Analytical
-C · Execution
-D · Communication
-E · Creative</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Learning+1
-B · Analytical+3, Learning+2
-C · Execution+3, Learning+1
-D · Communication+3, Leadership+1
-E · Creative+3, Execution+1</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Technology, Life Sciences &amp; Medicine, Agriculture, Law &amp; Social Sciences</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>AI Developer, Biotechnologist, Agronomist, Constitutional Lawyer</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="112" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Q38</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Your class must create a digital platform for Indian students. What primary feature do you design?</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>An AI algorithm that solves complex study problems.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Mental health counselling &amp; wellness tracker tools.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>An interactive portal on civic rights, duties, &amp; legal awareness.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>A pocket-money management &amp; micro-investing simulator.</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>A creative showcase where students publish art, writing and film.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Technical, Psychological, Civic/Legal, Financial</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>A · Technical
-B · Psychological
-C · Civic/Legal
-D · Financial
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Relationship
-C · Communication
-D · Execution
-E · Creative</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Creative+1
-B · Relationship+3, Analytical+1
-C · Communication+3, Learning+1
-D · Execution+3, Analytical+1
-E · Creative+3, Communication+1</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Technology, Allied Health &amp; Psychology, Law &amp; Humanities, Finance &amp; Business</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Systems Architect, Clinical Psychologist, Legal Advisor, Financial Planner</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="112" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Q39</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Your team enters an Inter-School Community Project competition. Which role do you pick?</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Mechanical/Tech Lead: Building &amp; repairing hardware tools.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Medical &amp; Wellness Lead: Managing first-aid &amp; health checkups.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Environmental Lead: Designing tree plantation &amp; soil care plans.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Strategy &amp; Finance Lead: Budgeting, sponsorship, &amp; pitch decks.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Communications Lead: documenting the project and presenting it publicly.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Mechanical, Medical, Environmental, Strategic/Financial</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>A · Mechanical
-B · Medical
-C · Environmental
-D · Strategic/Financial
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>A · Execution
-B · Relationship
-C · Execution
-D · Leadership
-E · Communication</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>A · Execution+3, Analytical+1
-B · Relationship+3, Execution+1
-C · Execution+3, Creative+1
-D · Leadership+3, Analytical+1
-E · Communication+3, Creative+1</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Engineering &amp; Robotics, Healthcare, Agriculture &amp; Ecology, Commerce &amp; Finance</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Mechanical Engineer, Paramedic / Doctor, Forestry Officer, Chartered Accountant (CA)</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Q40</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>If you could shadow a top professional for one week, who would you choose?</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>A Lead Developer coding AI applications at a tech giant.</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>A Surgeon performing precision operations in a hospital.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>An Agricultural Scientist developing drought-resistant crops.</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>A Corporate Lawyer defending major international clients.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>A Creative Director running a design and film studio.</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Analytical/Tech, Diagnostic/Medical, Biological/Agri, Logical/Legal</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical/Tech
-B · Diagnostic/Medical
-C · Biological/Agri
-D · Logical/Legal
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Execution
-C · Learning
-D · Communication
-E · Creative</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Learning+2
-B · Execution+3, Analytical+2
-C · Learning+3, Adaptability+1
-D · Communication+3, Analytical+1
-E · Creative+3, Leadership+1</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>STEM &amp; Software, Medical Sciences, Agriculture &amp; Bio-Tech, Law &amp; Corporate Services</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Surgeon, Agronomist, Corporate Advocate</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="112" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Q41</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Your school newsletter needs a special dedicated column. Which section do you write?</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Tech Byte: Future AI gadgets, coding, &amp; space discoveries.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Body &amp; Mind: Disease prevention, health tips, &amp; sports nutrition.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Earth Watch: Climate action, sustainable farming, &amp; wildlife.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Money &amp; Markets: Stock market basics, saving tips, &amp; startups.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Stage &amp; Screen: film, music, design and student creative work.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Technical, Health/Biological, Ecological, Financial</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>A · Technical
-B · Health/Biological
-C · Ecological
-D · Financial
-E · Creative/Media</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical
-B · Relationship
-C · Learning
-D · Analytical
-E · Creative</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>A · Analytical+3, Communication+1
-B · Relationship+3, Communication+1
-C · Learning+3, Communication+1
-D · Analytical+3, Leadership+1
-E · Creative+3, Communication+1</t>
+E · Creative+3, Learning+1</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Science &amp; Tech, Healthcare, Agriculture &amp; Environment, Business &amp; Economics</t>
+          <t>Quality, Finance, Media, Education</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist, Nutritionist / Physician, Wildlife Biologist, Investment Banker</t>
+          <t>Auditor, Chartered Accountant, Journalist, Teacher</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>working-style rebuild</t>
         </is>
       </c>
     </row>
@@ -4874,83 +4776,79 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>A sudden emergency occurs during a school trip. What is your immediate instinct?</t>
+          <t>Next year you could give up your Saturdays to one thing. Which would you choose?</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fix malfunctioning communications or transport gear.</t>
+          <t>Finish something big I can point at.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Provide immediate first-aid &amp; assess physical symptoms.</t>
+          <t>Get properly good at one hard skill.</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Consult rules, safety guidelines, &amp; legal protocols.</t>
+          <t>Run something, and own what goes wrong.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Manage food/water resources &amp; organize logistics calmly.</t>
+          <t>Help people who need it, unglamorously.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Keep everyone calm and handle communication with the group.</t>
+          <t>Speak well enough that a room listens.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Technical, Medical, Administrative, Operations</t>
+          <t>Execution, Learning, Leadership, Relationship, Communication</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>A · Technical
-B · Medical
-C · Administrative
-D · Operations
-E · Interpersonal</t>
+          <t>A · Execution
+B · Learning
+C · Leadership
+D · Relationship
+E · Communication</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>A · Execution
-B · Execution
-C · Analytical
-D · Execution
-E · Relationship</t>
+          <t>A · Delivering
+B · Reasoning
+C · Persuading
+D · Connecting
+E · Persuading</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>A · Execution+3, Analytical+1
-B · Execution+3, Relationship+2
-C · Analytical+3, Execution+1
-D · Execution+3, Adaptability+1
-E · Relationship+3, Communication+2</t>
+B · Learning+3, Analytical+1
+C · Leadership+3, Execution+1
+D · Relationship+3, Adaptability+1
+E · Communication+3, Leadership+1</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Core Engineering, Emergency Medicine, Law &amp; Compliance, Operations &amp; Supply Chain</t>
+          <t>Integrated validation — all career clusters</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Operations Engineer, Emergency Doctor, Hospital Administrator, Supply Chain Head</t>
+          <t>Engineering, Healthcare, Business, Design, Education, Public Service</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>working-style rebuild</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4861,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Construct warning. Across all 8 items the options differ by SUBJECT (tech / health / agri / law / finance), not by working style, and each option is prefixed with its own label, which tells the student what it measures. That makes this section a second career-interest scale rather than a strengths scale. The 'Strength Domain (engine)' column is DERIVED from each option's action verb so the eight-domain scoring still runs, but it is approximate — a strengths section normally varies the action (analyse / create / lead / organise / persuade) while holding the subject fixed.</t>
+          <t>Each item is one scenario; the five options are different ways of responding to it, so the section measures working style rather than subject preference — the previous version varied the subject and duplicated the Interests scale. Every option carries a cost (covering for a teammate means resenting it; arguing your case means annoying the teacher; asking for help means looking clueless), so there is no flattering answer to pick without thinking. Scored on the eight domains the career map already uses, and rolled up to four reporting groups: Delivering, Persuading, Connecting, Reasoning.</t>
         </is>
       </c>
     </row>
@@ -5074,74 +4972,74 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>School gives opportunity to select one special project for the entire year. Which would excite you most?</t>
+          <t>One thing your next two years are really about. Which?</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Challenging project to improve skills and achieve excellent results</t>
+          <t>Being the best at one thing, and narrow.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Create something completely new nobody has tried</t>
+          <t>Making something new that may not work.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Solve a problem faced by people or society</t>
+          <t>Learning one field properly, slowly.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Lead a team and make key decisions to achieve the goal</t>
+          <t>Running things, and being blamed for them.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>A well-defined project with clear steps and a dependable result</t>
+          <t>A steady path with no surprises.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Achievement, Innovation, Impact, Leadership, Security</t>
+          <t>Achievement, Innovation, Learning, Leadership, Security</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>A · Achievement
 B · Innovation
-C · Impact
+C · Learning
 D · Leadership
 E · Security</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement+3, Innovation+1, Learning+1
-B · Innovation+3, Achievement+1, Impact+1
-C · Impact+3, Innovation+1, Leadership+1
-D · Leadership+3, Achievement+1, Impact+1
-E · Security+3, Achievement+1</t>
+          <t>A · Achievement+3, Learning+1
+B · Innovation+3, Achievement+1
+C · Learning+3
+D · Leadership+3, Achievement+1
+E · Security+3</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Engineering, Research, Design, Healthcare, Entrepreneurship, Management</t>
+          <t>Engineering, Research, Design, Healthcare, Management</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Engineer, Scientist, Doctor, Entrepreneur, Project Manager</t>
+          <t>Engineer, Research Scientist, Product Designer, Doctor, Project Manager</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>A · trade-off rewrite
+B · trade-off rewrite
+C · trade-off rewrite
+D · trade-off rewrite
+E · trade-off rewrite</t>
         </is>
       </c>
     </row>
@@ -5153,74 +5051,74 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Extra time after school. Which activity would feel most satisfying?</t>
+          <t>A free hour every day for a year. What do you do with it?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Practicing a skill to get better at it</t>
+          <t>Help someone who cannot repay it.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Exploring new ideas, experimenting creatively</t>
+          <t>Get ahead so nothing piles up.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Helping someone learn or solve a problem</t>
+          <t>Build something nobody asked for.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Organizing a group activity</t>
+          <t>Study something hard with no reward.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Getting ahead on work already scheduled, so nothing piles up</t>
+          <t>Organise people, and handle the fallout.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Achievement, Innovation, Impact, Leadership, Security</t>
+          <t>Impact, Security, Innovation, Learning, Leadership</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement
-B · Innovation
-C · Impact
-D · Leadership
-E · Security</t>
+          <t>A · Impact
+B · Security
+C · Innovation
+D · Learning
+E · Leadership</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement+3, Learning+2
-B · Innovation+3, Learning+1
-C · Impact+3, Learning+1
-D · Leadership+3, Achievement+1
-E · Security+3, Achievement+1</t>
+          <t>A · Impact+3
+B · Security+3, Achievement+1
+C · Innovation+3, Learning+1
+D · Learning+3, Achievement+1
+E · Leadership+3</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Technology, Education, Healthcare, Business, Creative Fields</t>
+          <t>Education, Technology, Healthcare, Business, Creative Fields</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer, Teacher, Doctor, Designer, Business Leader</t>
+          <t>Teacher, Software Engineer, Doctor, Business Manager, Graphic Designer</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>A · trade-off rewrite
+B · trade-off rewrite
+C · trade-off rewrite
+D · trade-off rewrite
+E · trade-off rewrite</t>
         </is>
       </c>
     </row>
@@ -5232,60 +5130,60 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Achieved success in your future career. What would make you most proud?</t>
+          <t>Twenty years on, what would you want said about your work?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Becoming highly skilled, recognized as an expert</t>
+          <t>It made life better for people.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Creating something innovative that changes how people do things</t>
+          <t>It was the best in its field.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Making a meaningful difference in people's lives</t>
+          <t>It ran because I held it together.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Becoming a leader who influences important decisions</t>
+          <t>It lasted, and never let anyone down.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Building a secure, stable career that supports my family well</t>
+          <t>It did not exist before.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Achievement, Innovation, Impact, Leadership, Security</t>
+          <t>Impact, Achievement, Leadership, Security, Innovation</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement
-B · Innovation
-C · Impact
-D · Leadership
-E · Security</t>
+          <t>A · Impact
+B · Achievement
+C · Leadership
+D · Security
+E · Innovation</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement+3, Learning+2
-B · Innovation+3, Achievement+1
-C · Impact+3
-D · Leadership+3, Achievement+1
-E · Security+3, Impact+1</t>
+          <t>A · Impact+3
+B · Achievement+3, Learning+1
+C · Leadership+3
+D · Security+3, Achievement+1
+E · Innovation+3</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Research, Technology, Healthcare, Social Services, Government</t>
+          <t>Research, Technology, Healthcare, Public Service, Government</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5295,11 +5193,11 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>A · trade-off rewrite
+B · trade-off rewrite
+C · trade-off rewrite
+D · trade-off rewrite
+E · trade-off rewrite</t>
         </is>
       </c>
     </row>
@@ -5311,74 +5209,74 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>School competition where students choose their own challenge. Which would you prefer?</t>
+          <t>Two offers, same pay. Which do you take?</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Difficult challenge to test abilities, compete with others</t>
+          <t>Predictable, safe, a bit dull.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Creative challenge to design something unique</t>
+          <t>Hard, and I would be out of my depth.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Challenge that helps improve school or community</t>
+          <t>In charge, with the pressure that brings.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Challenge to coordinate and manage a team</t>
+          <t>Free to experiment, might go nowhere.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>A challenge with clear rules where I know exactly what is expected</t>
+          <t>Useful work, barely noticed.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Achievement, Innovation, Impact, Leadership, Security</t>
+          <t>Security, Learning, Leadership, Innovation, Impact</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement
-B · Innovation
-C · Impact
-D · Leadership
-E · Security</t>
+          <t>A · Security
+B · Learning
+C · Leadership
+D · Innovation
+E · Impact</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>A · Achievement+3, Learning+1
-B · Innovation+3
-C · Impact+3
-D · Leadership+3
-E · Security+3, Achievement+1</t>
+          <t>A · Security+3
+B · Learning+3, Achievement+1
+C · Leadership+3
+D · Innovation+3, Learning+1
+E · Impact+3</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Sports, Engineering, Design, Social Impact, Management</t>
+          <t>Finance, Research, Management, Design, Public Service</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Athlete, Engineer, Designer, Social Worker, Manager</t>
+          <t>Chartered Accountant, Research Scientist, Operations Manager, Product Designer, Social Worker</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>A · trade-off rewrite
+B · trade-off rewrite
+C · trade-off rewrite
+D · trade-off rewrite
+E · trade-off rewrite</t>
         </is>
       </c>
     </row>
@@ -5390,74 +5288,74 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Choosing your future workplace — which environment would motivate you most?</t>
+          <t>A year from now, what would make it a year well spent?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Continuously learn, improve, achieve bigger goals</t>
+          <t>I got much better at something hard.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Freedom to explore ideas and try new approaches</t>
+          <t>People followed a decision I made.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Work that helps people, creates positive change</t>
+          <t>I beat a target I set myself.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Stability, clear systems, structured career path</t>
+          <t>Someone's life is measurably better.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>A place where I can take charge of a team and be judged on results</t>
+          <t>I built something from nothing.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Learning, Innovation, Impact, Security, Leadership</t>
+          <t>Learning, Leadership, Achievement, Impact, Innovation</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>A · Learning
-B · Innovation
-C · Impact
-D · Security
-E · Leadership</t>
+B · Leadership
+C · Achievement
+D · Impact
+E · Innovation</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>A · Learning+3, Achievement+2
-B · Innovation+3, Learning+1
-C · Impact+3
-D · Security+3
-E · Leadership+3, Achievement+2</t>
+B · Leadership+3
+C · Achievement+3
+D · Impact+3
+E · Innovation+3</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Research, Entrepreneurship, Healthcare, Education, Finance, Government</t>
+          <t>Research, Entrepreneurship, Healthcare, Education, Government</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Scientist, Startup Founder, Doctor, Teacher, Banker, Civil Servant</t>
+          <t>Research Scientist, Startup Founder, Doctor, Teacher, Civil Services Officer</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>A · finalised set 2026
-B · finalised set 2026
-C · finalised set 2026
-D · finalised set 2026
-E · 5th option added</t>
+          <t>A · trade-off rewrite
+B · trade-off rewrite
+C · trade-off rewrite
+D · trade-off rewrite
+E · trade-off rewrite</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5482,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Use a mix — see it, talk it through, then practise it</t>
+          <t>Work through a solved example first, then try one myself</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -5650,7 +5548,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Mix diagrams, discussion, notes and practice depending on the subject</t>
+          <t>Test myself on past questions and fix whatever I get wrong</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5716,7 +5614,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Switch between watching, asking, reading and trying as I go</t>
+          <t>Copy someone doing it step by step until it clicks</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -5782,7 +5680,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Use all of them — videos, talks, reading and a real visit</t>
+          <t>Spend a day shadowing someone and judge it from how it felt</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
